--- a/downloads/receipt links.xlsx
+++ b/downloads/receipt links.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="477">
   <si>
     <t>expense_id</t>
   </si>
@@ -46,37 +46,148 @@
     <t>blob</t>
   </si>
   <si>
+    <t>txZONeYTGMhM</t>
+  </si>
+  <si>
+    <t>fi6DqtSpQQxB</t>
+  </si>
+  <si>
+    <t>dominos_Nov_05_2025.png</t>
+  </si>
+  <si>
+    <t>RECEIPT</t>
+  </si>
+  <si>
+    <t>image/png</t>
+  </si>
+  <si>
+    <t>usxGgLmlhGIn</t>
+  </si>
+  <si>
+    <t>ou3buQtZatb1</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6DqtSpQQxB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlJIRjBVM0JSVVhoQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5BdnFISnlXeklpN1ExT3ZWVUlDVzlVTFBOYl9kX0VXeTNDVVlBdVJlN21LUnZOdnVaVVJ6SWt1YVFjS1dTc1QyQ2dFeXNjT0FlSjNjY0tZSDc4M1I4dw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>1772183414</t>
+  </si>
+  <si>
+    <t>1773479414</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>txwCBf0vxiTB</t>
+  </si>
+  <si>
+    <t>fimbazDdoan6</t>
+  </si>
+  <si>
+    <t>amazon_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fimbazDdoan6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdFltRjZSR1J2WVc0Mklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5ZM1A3SkdkY0VpWG0yRWR5X1NQbmZnbmE0dFEwY3lTeF9OS0h3QWN3UTlRc2g2eUhKQ05RbU1vT3QycHlPcTBOeEZ1WXBtRHp1QXNqY242bjJoek1GZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>txvD8YnSeMMb</t>
+  </si>
+  <si>
+    <t>fiQc4Ng1RRK8</t>
+  </si>
+  <si>
+    <t>marriott_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiQc4Ng1RRK8&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUll6Uk9aekZTVWtzNElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5TRWxzOWVuUWg0ZTR0elUzbWhjVjZPWGNtUGlnbmF1c0NuX1V3eXpxSXc1ZXBLNkhsUi1rR0dDaVQyT01XWmxPZDJuanJGRDU2ZHNHR1FlVzRXQmdtdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>txZDF9PjEj3o</t>
+  </si>
+  <si>
+    <t>fib4h01PgYUA</t>
+  </si>
+  <si>
+    <t>staples_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fib4h01PgYUA&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saU5HZ3dNVkJuV1ZWQklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC53UTBhaFhicXBUUEx5Nk83ODhzZGVSZzlEMmdKQUhwVUNobnZyQ0o4cjlVcmYxaTBhQThSdUVEMTZiSWNFRFV3ZUxPajY3cU1DRFVNOWhkcnZfdGhHZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>tx6rtotdbaqd</t>
+  </si>
+  <si>
+    <t>fiWC95WYgH7K</t>
+  </si>
+  <si>
+    <t>extension.pdf</t>
+  </si>
+  <si>
+    <t>application/pdf</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWC95WYgH7K&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFF6azFWMWxuU0RkTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC51blFHQ3ozT3JTclA3UnQ5Z0N2QjhXdGJoVnJvRUthcWNTclFDZTI4WmQ5dkc3QXJab3VWbEd1SlZMaGhuREJxY0ZkaHluUmFMaTZNS0VYZDRYRGxJUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>fiWlWI0d4RYo</t>
+  </si>
+  <si>
+    <t>taco_251116pf00802583_cd238f9d3d4b4f3aaeaa9ccf94e1eda9.pdf</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWlWI0d4RYo&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWGJGZEpNR1EwVWxsdklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5lS1RtVDRVeF9TTk9MNVRCVTBZSUw1ZlNvQ0JIa2UzVFR6X3Y2WktzWVg4ek5xU1VzWmhXMVM4eG5ueHNZSDJQTjAwd19PQjhqRDhJMk5hNUZfeVI1UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>txMDepeX0kkO</t>
+  </si>
+  <si>
+    <t>fiUAGZoUsr1n</t>
+  </si>
+  <si>
+    <t>lyft_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiUAGZoUsr1n&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVlFVZGFiMVZ6Y2pGdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5ObTVoN1lrRVk2Nk9VdzdxRlVqQ3BlMXA0UHk5M2pXZU1lT21ZV1NNbmNFMzFoSll2MVBJcUhjd0ZxcXlCSTl4MEs1OVRGRUhPdEpzNGp4b3F5NFFiUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>txBKBOkRqvmR</t>
+  </si>
+  <si>
+    <t>fiaLtjj1hBH4</t>
+  </si>
+  <si>
+    <t>uber_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiaLtjj1hBH4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saFRIUnFhakZvUWtnMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5OdTZ1Q1VqX3FXOWVZRVUxaWRLdE9tczNrSVZfbHlraVNDM2xyWnZJcmFDQ052QzNYMEE3TkQ4RnhSWU5JWE55bDRkTEsyeHZmclUxa0xrMTR0WGM5QQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
+    <t>tx3XbGNiTOTU</t>
+  </si>
+  <si>
+    <t>fi5n0m9PkGSn</t>
+  </si>
+  <si>
+    <t>dominos_Nov_25_2025.png</t>
+  </si>
+  <si>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5n0m9PkGSn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMWJqQnRPVkJyUjFOdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CenpZcUtkX1p1OFlJdVREalhjekkxMVhrbWZaazlDQk1pc3Z4eU9BMjZ4OEFxbXRBZ0RnczFraEx5R2ZFVmtYWUtKa0RCbEpSZ2NIRWhHbXgxUnFwZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
+  </si>
+  <si>
     <t>txVnxp46ZpIu</t>
   </si>
   <si>
     <t>fipWgaI1P89R</t>
   </si>
   <si>
-    <t>lyft_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>RECEIPT</t>
-  </si>
-  <si>
-    <t>image/png</t>
-  </si>
-  <si>
     <t>usyXAERqjQGX</t>
   </si>
   <si>
     <t>ouHelfvTOEYt</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipWgaI1P89R&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1YyZGhTVEZRT0RsU0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5fbW1mRnpxXzNCamJEWUR5blhqVnJxeENZZjJiWmhFUU5aT19HbjF0dnE0Y0czMFlZeXZvam43TWJNUUhNc01NQTY1WlBjMFk5MjJTdGE5S1RXQUVyQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>1771851772</t>
-  </si>
-  <si>
-    <t>1773147772</t>
-  </si>
-  <si>
-    <t/>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipWgaI1P89R&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1YyZGhTVEZRT0RsU0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NV0dPWkNLLVFKSjZnSkdmaG9CYVdsdzV3V1hUN1lsMHAtLTZxVkpGclhZaFFCLVNWYWdxbG4xUjhUOXJ3MTF3T2p1Vm56QUdhd1l3elowYmU2T1EtQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txEmIYAmi2gA</t>
@@ -85,10 +196,7 @@
     <t>fiu43ggBqrX6</t>
   </si>
   <si>
-    <t>dominos_Nov_05_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiu43ggBqrX6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMU5ETm5aMEp4Y2xnMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC41NVNzcnNYMzlVSFJWR3U3dGxGaGFBOGJYV0VOV2R1WS1KdEZYbTV6ZEc3YlJjSHNQRjh6QTd6VkFUUzFVOUVGMEVCc3pjSmN1bEdhUWtBRmp6YUZhUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiu43ggBqrX6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMU5ETm5aMEp4Y2xnMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC54Z3QweUJmbmJlU2l0YkctellZZFl2aTlUS1pTSWhqaVpXdXg5OHRmNUhNY0dsM0cyUm5RbmdaVVA3em5xWm5WYW9NVHlfWHZ1ZUhIZWpLbm9rcF9wZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txRQU6y8eN1t</t>
@@ -97,115 +205,7 @@
     <t>fi6g9ZYnN9bk</t>
   </si>
   <si>
-    <t>dominos_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6g9ZYnN9bk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlp6bGFXVzVPT1dKcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5RejliMkRzVF9vMlhIMy1SZUFmdGhwbzBGS2tUcVVxVXdKczhKOXRKMS0zV0RTTlFlZ0Q4bmdrOVpDU2lvNmhXQ2F5c0h2WGxMdFFaeHREcUtCMk5YZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txZONeYTGMhM</t>
-  </si>
-  <si>
-    <t>fi6DqtSpQQxB</t>
-  </si>
-  <si>
-    <t>usxGgLmlhGIn</t>
-  </si>
-  <si>
-    <t>ou3buQtZatb1</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6DqtSpQQxB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlJIRjBVM0JSVVhoQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5lVmZFN2ZDSjc1dU5Hc3ljNDlBUXF3SGJxbDdCVURYR25wSGNGX3doZ3RTanYtdXotVHhHNE5JQ1U3MEtLa1RXZGJzcWdZcmVQN3B1bS1KWnRvQ1lRdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txwCBf0vxiTB</t>
-  </si>
-  <si>
-    <t>fimbazDdoan6</t>
-  </si>
-  <si>
-    <t>amazon_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fimbazDdoan6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdFltRjZSR1J2WVc0Mklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5XWk1NSFE2czRfTGdDWWo3dWx3bGVFY0U2R0NFYnRLMktTRHZYdHY2Y19jTk5peFIzTGdZMklUV1hQdEVBRFJZdVR2ZXBtb3plYUp6MEozYXhGY2VLQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txvD8YnSeMMb</t>
-  </si>
-  <si>
-    <t>fiQc4Ng1RRK8</t>
-  </si>
-  <si>
-    <t>marriott_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiQc4Ng1RRK8&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUll6Uk9aekZTVWtzNElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5XUjgzNHFHSVYyckRYVmFpcTl0bHE1TVFrNWthWGEwbFBIcmlsVzRsZTJENnBTRE9pNExoUDh4QVI0SHk5LWFJVGxZNlZQNVhxRFZhT2hhQXlWdnJ4Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txZDF9PjEj3o</t>
-  </si>
-  <si>
-    <t>fib4h01PgYUA</t>
-  </si>
-  <si>
-    <t>staples_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fib4h01PgYUA&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saU5HZ3dNVkJuV1ZWQklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5zWE5aWUVwVVluUWdRQm14TG9Bbnhvcm9QY3oyTTV5WlViVUxyOU85ODlweTA1YnVsMDM5dzNBZ0pfVWp6R1IyMGRtemNnVDNuLS1sNC1pUWsyZ01UZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>tx6rtotdbaqd</t>
-  </si>
-  <si>
-    <t>fiWC95WYgH7K</t>
-  </si>
-  <si>
-    <t>extension.pdf</t>
-  </si>
-  <si>
-    <t>application/pdf</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWC95WYgH7K&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFF6azFWMWxuU0RkTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5SanVTSnI5Unp3RnJId1NMdFVSTDJ6d3BTMnN2d3pyY3JQdWNPQ290ZXRqQmhSd3dvZ2dYVG9DejlsYU5VX0p1blNkUUdGOE5Qc3l5ek5WeVFXYjJ2UQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>fiWlWI0d4RYo</t>
-  </si>
-  <si>
-    <t>taco_251116pf00802583_cd238f9d3d4b4f3aaeaa9ccf94e1eda9.pdf</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWlWI0d4RYo&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWGJGZEpNR1EwVWxsdklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5zV3lFdlh1RGlCczV0eVFmdkdHWFBjYkw1RklwU0duT3NHNUYyZUUwUXc4S0RiMThiZENUMmluRkhDV3IwNmJ2Y1JuMnZIQlQtNHNDVENGVFpUVnJNQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txMDepeX0kkO</t>
-  </si>
-  <si>
-    <t>fiUAGZoUsr1n</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiUAGZoUsr1n&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVlFVZGFiMVZ6Y2pGdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC44UWp2N0hTNEdCd05HQ0NGTlRqSHRWbERvRXBRclhQRkd3aUE4TXJPamVWd2NKdTFVb2I2S2pYNmtPdW5WYjRiaHlGaVk2LVZQSUVadUlhdXlyRmd3Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>txBKBOkRqvmR</t>
-  </si>
-  <si>
-    <t>fiaLtjj1hBH4</t>
-  </si>
-  <si>
-    <t>uber_Nov_25_2025.png</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiaLtjj1hBH4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saFRIUnFhakZvUWtnMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5jakQ3TFhTRTF2Mi1kbmZOelFQblZnc0dmaVYycDM3aHlyQ1FHR1VRNVNtMlNZbnRRVUowaGhQRTNIVVFVVnRpV1ZsWEVsVGVoRU5HMHdsVnRZTjY4dw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
-  </si>
-  <si>
-    <t>tx3XbGNiTOTU</t>
-  </si>
-  <si>
-    <t>fi5n0m9PkGSn</t>
-  </si>
-  <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5n0m9PkGSn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMWJqQnRPVkJyUjFOdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5RUVZaMzA0dnFnYXdGYWEwY1RBMEZ5THVkV2FYZUdqdTFxNTU5Y0h5VXM3eWY3M1FGeUp5MmdNTkFiUE9SV0dzVUhCcWd5TGlTSUlmeTJFeVpwNjJWdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6g9ZYnN9bk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlp6bGFXVzVPT1dKcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5hQVNkcV9FUkVxSU04dzQ2UW41ZXVuWjQtNDNOdnNKSlo2MnI0b0hvbFNlNzJQTmZPYkhZVWFNUlR1TVE0cWR0UFNRcTVtblg4bl9RZVZ6TWM4em03Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txyL0yI2g8bT</t>
@@ -217,7 +217,7 @@
     <t>mileage_map.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieDWalgOklQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFJGZGhiR2RQYTJ4Uklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC52TGo0Vm5nanBsMy1GbHRqZTJmMDRSNXJ1Z3lwU2xiQ2tLcENaZlZ1OEp3d200WWIxQmNuSlhQaWtNeGExVnJ0RVZzaUtMVEZ2bzNxT0ozeTRPMFU5QQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieDWalgOklQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFJGZGhiR2RQYTJ4Uklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5EUEpaeXZ6NmIyaEQxdDFacXJkU180anZrTjBhSDZCeUg0aXJNVVppbHRaZTBjZWVKYjFyMzRCM0hwS0p5MGV4X2pSMENqd0NaRndCSTNyOVhKMU1sZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txGrmZmnhmmd</t>
@@ -226,7 +226,7 @@
     <t>fioyWGa3UIog</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioyWGa3UIog&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmVWZEhZVE5WU1c5bklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5FTzFZWmhkcGoxZWVYdWpqSnQ0ek5LZUR6TjQxQ2d4ZzVBdGRYSDVIajRfZDUzVkxvblNNSjhOZ01MU1NidjFxcWpBdmFZa2hWUHNKZ01ZSktFajBCZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioyWGa3UIog&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmVWZEhZVE5WU1c5bklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5FQnJtU1dIQnJaVmdMRm5jSkQ5djg4OUp6YVR3VWYtNFdZT3o2azcwYmV4cV85bG43VEFUX1VkeVZOUGNVVTB0VEpYaF84MGJacGFRaDZqX29idUNodw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txWcCAQeSDKO</t>
@@ -238,7 +238,7 @@
     <t>uber_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiJvU5PwIRKx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sS2RsVTFVSGRKVWt0NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5sM05ucUVCNUtTVWVFMmFpTWZ6WFppekpuVDNEY24zOFZ0LUxoNzE3QXpzbnZQTWtCOHdtUlF4NFNDeGNkdUQ3dnc4VXFzRmF3YjItanZEYWp3dTN2UQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiJvU5PwIRKx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sS2RsVTFVSGRKVWt0NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC54V0hFb25sUHJfV2F1b2htdHlLNG9kX1FKSGVvbmJYUFdFZk8tZ3hEc0tKQ3g4cGt1Znp6eEg3RlBJdjFTTFppT0Q3Rks2VnBsdXY5V2VSdUFnY3Y0Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx3SijjE7S86</t>
@@ -247,7 +247,7 @@
     <t>fi0NCd20xhAl</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi0NCd20xhAl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rd1RrTmtNakI0YUVGc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5rdzdKbzgyMTJpTjJQWUZFd2M3b3R5YnI5NjZPRlZDMmgtc2lmVWlQQlU2UVR3SEpfUHFMVldrSklpS19wV0JqbGNKaDhTczdkbTBfbWNZb21qTXIxQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi0NCd20xhAl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rd1RrTmtNakI0YUVGc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5HVEU1c3VUUllodGxLY1NfVUFPR2lmaDRLem02ZEJqYktqTk9xeXYtakREZWFaN2lhQ2taN1lneU9MaTZ5VDE5cGxmLV9WZERaUExPWk9uVGxlQ1ltZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx85OfVEfQCw</t>
@@ -256,7 +256,7 @@
     <t>filOCev8tgNE</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=filOCev8tgNE&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sc1QwTmxkamgwWjA1Rklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5UNkVMZkE1bGVsUUFEdDVheHJHNjBWWWdTTUpGcmxEMU9sTE15UVpCaU9seTVzOEFrTmdUY0FhNjd2aWlHUEcxNm9BYWNXblZNaXIxbjF0UXlpUy1Pdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=filOCev8tgNE&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sc1QwTmxkamgwWjA1Rklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5GSW9sQjVDTWRDYlZEaUxtWVlCVDgxNWVDTXZPTEFXU1VMTmRPLUxRaG1XQ05jbEFUcU9UbV9JWi1xNFRnLWxFMlpEdmc3M2dGaDd1TEFNaXdrX1NuZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txOH8SZk5UZ4</t>
@@ -268,7 +268,7 @@
     <t>amazon_Nov_09_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2d9Ox8nBGk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVpEbFBlRGh1UWtkcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5Pank3QXh3bUlSNUdXRW43THBQdEVGTnpscnBPM1NodWd3R2N6U1BLYURYVklSb1BQZ0pIeVhDQWdtNmRPTFZvekpuVVM2VzBqaTN4Zmo2THJPSkljUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2d9Ox8nBGk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVpEbFBlRGh1UWtkcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5DMzZ4c3g2RE80d3JKOTdwTi1kRW1sUlJUMzIxNWpIQ09CSHhzSEZ6SzJ3bHg2ZXpySTZtaWxmRGZVbkRyZDdZQU5NcVM2RjRHVGFFa24wd0VpWEtnUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txjN0djNH1db</t>
@@ -280,7 +280,7 @@
     <t>marriott_Nov_09_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fir2i3XU0gOn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seU1ta3pXRlV3WjA5dUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5xMkhVVmVKaHprN1NkM2ZJbmR1eVU3MlBZZnJxNGtRYjlibEl6V1lWYWdUWktOZnlNZmVzQzJSbE44dnR0SDNSc3J2c2pxaV9ZMWlEc2J4WlZWb0RaQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fir2i3XU0gOn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seU1ta3pXRlV3WjA5dUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5odFdfcS1YSExscnVpck45WTczc1ZISy1DV1IwOG94UWg2VnBhdVBhb3lncl9HUWkyVDJlZlJsVnpNWnZ3SUY0eGNYSXVHUE5QbURqckdmdERxNWFiUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txtifbYkzmee</t>
@@ -292,7 +292,7 @@
     <t>dominos_Nov_09_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitcQjMmEe0u&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMFkxRnFUVzFGWlRCMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5QNzQtLW43N0tYRldFYVYzOUsyd1B4enFQYjVUdG1aX3RjQ1Z3cjVadlNIZDFIQTF4X1JVLTZUVHliY0hEUHRMVjY3SjNzN0QxREpMcW0wWC1DMDRYUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitcQjMmEe0u&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMFkxRnFUVzFGWlRCMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5mRTZJX2c0aDNIcmFsLW1sX1RDZzZlUzc3QS1Sbk9taTdPRmZ6SFNGNFVRN19zVW9jVEFlZ0xTeEFyR1cyQ3dueFhFR3pBT1Q2YkhHNXl5NzB2NlptUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx9oedvJQfvQ</t>
@@ -304,7 +304,7 @@
     <t>staples_Nov_09_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6feqRugsVu&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlptVnhVblZuYzFaMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5zeWpleHhvQmRJNVBLYU9GRzlFQlpGTjVmQVdRM3FXa0pjU1NZR0stNHFVWTdBZUFUMlc1Nkp2N3BCYWU3VVdvT3Vad0FMMW5yV0RhVUJoampkdVhSdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6feqRugsVu&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlptVnhVblZuYzFaMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC43bTJBeXlVM3VBQ0VyQTJkZ0l0dFBmeUQ5bWN0SnFJNEtjaTlKbmdSVmFIWUdGdk1JcWF3TDJhOGZ5VkdSMzU3ZlJrdC01V2FQZHg3ZVdNVjIxMHVXZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txr2AYydKTaK</t>
@@ -316,7 +316,7 @@
     <t>marriott_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiq9MB0RUyzv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seE9VMUNNRkpWZVhwMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC45ZFY5MDNpSGZubDItalY5VEViMEJUWWlvbVhzWkVBU3I1TFRVWDZrVDlpY3lZaXBnUDduUHRsdXgyRC1TQnhXYjVOcVZxa21CYlFoUUt3T1ZHTmpCZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiq9MB0RUyzv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seE9VMUNNRkpWZVhwMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CWlFtM1dzLVEtbUVJYVNLUzdTNlJ1bWd0QThQRElVT0swOXJ0VUYxajJqaHkza3NkeEduM1JncUVtcnNtSHdPWVh4Ujh4OERlbzV3clhyaFRPOGh0dw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txFey8QzIQyL</t>
@@ -328,7 +328,7 @@
     <t>lyft_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiwEgw9YY8KC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sM1JXZDNPVmxaT0V0RElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5pSnBJS2VycUo1bmdtZUdyTlozNEJpUkt5QUxEVG1zcTkxNFFEY3BVM0FOR3QzTWd6alhvUFdxV3BwR0VkWVZCRFl2TU9iNlQ3LXBrdExQa19hM25MUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiwEgw9YY8KC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sM1JXZDNPVmxaT0V0RElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5jakxoaHN4Tl83RmdZSHlzQlVsM3NrMS1xa1FNMVIta1pPUEdfMWlwazU5TzBFOFlPLVVTWndqcDNXNml6QlJPeUNrWUdFWWZTaHN0WmxiYldibWpuUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txW3QZS5R7il</t>
@@ -340,7 +340,7 @@
     <t>staples_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fij627Vzqf6N&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scU5qSTNWbnB4WmpaT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5RcE1KYkRtVms2aXBUcm11OWEzTnNkaXVoT3dRM2s4eGRkQlI5QXVjaFNhdTdRVC13Q2R4aXRqT2NiSFdSYThRQ0dDOF9hQVFONmJxRG1WaUt3VG5UUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fij627Vzqf6N&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scU5qSTNWbnB4WmpaT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC43RzdBNW14SHVRaFlMdWNiMm1YX19SWHNCaUZyUWhlTjNGUVN6YzVNVFcxNVhMZUt5N05UeUlXS1QzUlV3cnY3RnhicmJOTmxqNjB2dUFOT1VzS3ZTdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txguOMIBiqXr</t>
@@ -349,7 +349,7 @@
     <t>fiNp3TnhFJcq</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNp3TnhFJcq&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT2NETlVibWhHU21OeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC4zeWRXOGtNbV9sS1RtSHljMWVRU3YwamU0X2pZcFFzb0RWenlMQ0hvRWVGMFR1YzVjdkk3ZlhwV3VNX3dzS1RFZTMzRmJzV1Y3YWhLNXllcExYZGNUQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNp3TnhFJcq&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT2NETlVibWhHU21OeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5vdlRyZk5DQWpLUFZEV2M0OFFJM0x0ZEVQQTljRzJUd2FkeFhTRG00YmNteU9JTFZFQUF3NW1qM2VIRlg0OFU2TXdLeENBeUJYeE9RNFBYdS00VHJUQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txLiq5pahsp2</t>
@@ -358,7 +358,7 @@
     <t>fi6yqqqW6bTM</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6yqqqW6bTM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMmVYRnhjVmMyWWxSTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5sU3ZrLV9ZV0RsNTN2blhNTzRLOEFkb0Rjd0hlbjNNM1J6aUMwSXZLTVBxSkZGRU4yT2VpLXptNU9VcXlOTldUak9XblIzU19CWGdRMXVIZnJYNEdBZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6yqqqW6bTM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMmVYRnhjVmMyWWxSTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5PNkhxUFBXbDFyTnNxSmd3ajNVVW9RMnFVQk1QQV9HMVRVTm9PR3JZd1pYM0Nfc19iNG1lS0Ywa0hSVUhvRmdOellQLW1QUzdkTEhFQlc1UWJueUJLUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx9hGElDZLhP</t>
@@ -370,7 +370,7 @@
     <t>lyft_Nov_09_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5SR2cisFDl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVUxSXlZMmx6UmtSc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5sRmY2NEhyZzJhbHJ0ajJJbUJWei1SN3NvSzBMWXdJVk51WEVUeHRSVW5jdTUtTjFTU1o1YVVNQ0xwV1VHSG1MQVkzc25BYUtlMzhRZHlXeW5NX25MQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5SR2cisFDl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVUxSXlZMmx6UmtSc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5kWU9UWGk1bG1PdWsxbjRjYVQ4dUROSDB4cTktdjhmVjN3TXZDYllzZFlZOWRIRzJSNGxSZkZWd0s0ajhsUk94NmxiRUduY1dKLXNJMVZmZVhtdF94QQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txWwgKns1GLK</t>
@@ -379,7 +379,7 @@
     <t>fiP1tKqysA8w</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiP1tKqysA8w&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUU1YUkxjWGx6UVRoM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC4yVS1RT2F0M3pPNlNXTEQxalFvaDE1WGpPLXpVaC1CT20wNW1NU2EtT3ZzYkZMWTJ5bWx0ekdkRU5kSTZEVzBmSl95aWFqdzNsa1hwamlmZ0tHT004dw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiP1tKqysA8w&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUU1YUkxjWGx6UVRoM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56MDl0ZjVrZHc1V1dsaFJPSmc2ZXZvbXNhbVJQNzJ4YTlraUxBY0lpTVdQVjJ3azViekRZQTZ6RDgzbkZzOHRkUlRQMkhQTFlwMzdWSnRKaVRwNGZmUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txSvd6OrDiqq</t>
@@ -388,7 +388,7 @@
     <t>fi0CbhF7N4Yl</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi0CbhF7N4Yl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rd1EySm9SamRPTkZsc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5YYW90OTJZZ0lPbnoyRlowM2NpeXktMDRfNEZZeU1tRnd4ekpDUWluSC1aZlc2dVJvTHdUYTFSa1VDYWpJREc5bE5GdW5ZNC1EblFrNkJqWThkUzBzQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi0CbhF7N4Yl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rd1EySm9SamRPTkZsc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5kNHBsaEUwU3B6VTktbWUxNDI0Mndoc1pYRTZVRGkxS0tCYTBDRDhKUVZPOFNaZTAybXZzNWxTWm1TclpsZUp4SUNYdm9tUzY0Z010ZDNSbm5Jd19GQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txQcSSvmP1dC</t>
@@ -397,7 +397,7 @@
     <t>fizNOSOF7gLQ</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizNOSOF7gLQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlRrOVRUMFkzWjB4Uklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5GUktkMmwwVzlaTzV5STNBdHk5RldOS3E1WGVpc3RsQzR5V1dGSTFzRWNmdlpyZlpsd2hJREFJcVlRM1JVbjNBYVJzMGFWZllJN0xjNkN4XzNUb1VTQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizNOSOF7gLQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlRrOVRUMFkzWjB4Uklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5sYVUza0ZuTjZCTDFkN3V1eU9XOVhWRF85RWhydF9xV2QwZ1oyeUlSNG9VWFEwd19STWllRnlvcThZbEltVDUzVHJEdm43Y2hMb1JfbGlJbWk0eVBSUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txVliKWePihu</t>
@@ -409,7 +409,7 @@
     <t>amazon_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fivQVGtzLDpk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMlVWWkhkSHBNUkhCcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5aYWxzT3hnTTllXy0xeWk4U210djNMa2o5VkxNQUxFYjVndTVlR0ZOOW1yQURiOWtsUzl1NmliU0dPTm10QUtPbkRFbTVUZnJEUWRwNnJLdkY4YzNtZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fivQVGtzLDpk&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMlVWWkhkSHBNUkhCcklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5HTUY2ZnFOTkFKdFBnMk1XWUxnRVVBdThnVFFpRlRLSEhvUzFpTGw3V19Pd2RPa2xFLW9hcUhuRmpILUR6Y0F3WWVhSlR1Skg0bWhZeTVqUFZYVDhfdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx0BlZKZafTp</t>
@@ -418,7 +418,7 @@
     <t>fiAABQ4jkNz4</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiAABQ4jkNz4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQlFVSlJOR3ByVG5vMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5QZjczS2dZY19XajJPc05YMkszUTNrY0Zrc2s3blNvcDNpWW9Wd3NfbmpjRHBXN1YtOXdkTnA5RE1UZ0s5UTBqMFFUcDNmUVBsVlc2b01SUzB5TGY5Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiAABQ4jkNz4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQlFVSlJOR3ByVG5vMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5BdmF3anVnVzRlNTRHYklsZGRqNExoVTFTMzlTalZPLV9zQzdfM2Jjc1lEMF94NkxvXzZ5MGRlbE5VcDJYeHMxUDJxREhFdEp3bkVhbzdNbDdwMWh2UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txKJaiSpF9S2</t>
@@ -427,7 +427,7 @@
     <t>fiPu4VjvFi3N</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPu4VjvFi3N&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUWRUUldhblpHYVROT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5jaTZhdm9jQ0J3MFpHUFUzY3FzMndmRGFBS0NJWlhYUVFGMXg3N2lnT1JGREd3eWN2T3VxRWx5WGg2YTJnWWR4aTlCZkhYQmNRSGdheml6bmc5RDNydw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPu4VjvFi3N&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUWRUUldhblpHYVROT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5oVWtBMEM0MXI4QTM2SW94THk0M1ppSVRjSXVtMmc4WGJuaEFtNUNtLXJ0dVcyMnF5OXpjcDNKc3FWR2dMWGhHdm9QX21pcmNhUTJlMWFNcHZHbnVtQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx0UzPThQI5N</t>
@@ -436,7 +436,7 @@
     <t>ficOFy9MmKK1</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=ficOFy9MmKK1&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1salQwWjVPVTF0UzBzeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5lTFBrdG82RTZyQllqVDhwRmRROEV6ajVhV3duVDJ3Z2ZiOTZPdlQwZWJDNF93cXdsc3ZJb1Q5cC1HQ1V3REVKM0hSVDVKNWRVbTE1UWVodXJpNl9mZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=ficOFy9MmKK1&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1salQwWjVPVTF0UzBzeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5aTExsVUo3S2dBbzdJUVJQYnI2bktLRVAzLUxWUW14WnpNekpidl93N003Zm5OMFptNFlNRkZpR21vRmRxLWxwRTlTTVBjTUpvemJ3NmItQ0I4Mk5IZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txubsjYlUrVG</t>
@@ -445,7 +445,7 @@
     <t>fiBM4vrXEHg9</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiBM4vrXEHg9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQ1RUUjJjbGhGU0djNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5rZUdFMlRiYl82dFlzTFJzVVJjWWZidUt1bF9wZHFnWjFlX2ZiQ3Q2QlloSnpIRHBVWk5rbFpnWk91cnBGN2lFeDd0cnpieHBqVVV3U0c3SlJDNWZJQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiBM4vrXEHg9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQ1RUUjJjbGhGU0djNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5wQUF4b3c4Nzh0RjFBelpYc3U2bUE3em1ZQTh2V3NaVndYQ3Zmb0JlcGNEQmFjVklIRWliVHpsQXBKM2NMcHVub3JVTzhjRXliZnhZN0VIVndTTVZfQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txT6hnKTueLu</t>
@@ -454,7 +454,7 @@
     <t>fioiuFimWcnF</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioiuFimWcnF&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmFYVkdhVzFYWTI1R0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5vRWxrdHo4MzVpcThTaUtTYkJVUFh1emE3OExIcHdTNGFZbFprVVRiUXA0bm5qa3lSOUppMFJjQmxyMFMxdEtMUThoWTgtQTM1aXVuNXhBZFZvRmV6dw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioiuFimWcnF&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmFYVkdhVzFYWTI1R0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5OUkk1aXlYVUUzT0ljVk83WjFTWU9NdGlqQnNHZFE1cGZ3ZHFZd29sdm9yYjd4SHpKbm5oUGdRanMtQ1k5SU02dzh6TEdvS0JDOFllWDhTajJhbEludw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txGT5dGbwokd</t>
@@ -463,7 +463,7 @@
     <t>fieCQzj9NPkU</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieCQzj9NPkU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFExRjZhamxPVUd0Vklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5qNnRNSlBmanB0RFJVQlB3RzNRZVh0S19yRzVONWNRMVBEX3JHcW1FeDN5aER0YUc3QUszak0tMkFBbjFGaGNWQU9oVzB4WU1fdVBPTGJoek9qS3lkUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieCQzj9NPkU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFExRjZhamxPVUd0Vklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5VUFNiVGprTmswUm81LTNpMjd2clpyQnRudFE4aGlrR3pTSEtKdFhGUi1ja2E4NGw0MzNrQmdTWTc1TTVBblJUUTBsLWdXeFN0RG5BRVlYN1dRWVFSZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txLo79P9jrLo</t>
@@ -475,7 +475,7 @@
     <t>dominos_Nov_03_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi42Nahz3C7R&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rME1rNWhhSG96UXpkU0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5ybXFINjF5YUwyNlZkbWdrVzRUcmFkcnBRVWZZZWlLSmNoMHh2T2V0Q3dGZzhadUNIR0h3LV9zT0VWN1pqN185UjZoTnNzZU1rRGRwTlFoZ3RsRklTdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi42Nahz3C7R&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rME1rNWhhSG96UXpkU0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5MVnZMdXJuRENNNFdWeUxxMC1RdU9KVGlodkkzQkJnVmFmTmQzVUEydXZaSmsza2k3LWotS0ppUVF0ZHpoSnBmakRENGk5R1dqVGFnSkJyNnhxdF9vUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx5D6aphpAsT</t>
@@ -487,7 +487,7 @@
     <t>amazon_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiaeryA3aF7r&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saFpYSjVRVE5oUmpkeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC52ZUNrTW1kXzhXVFBPR3Fpekc1SDk3VXNVLW00SnVWWm9YamtjVFpPRUJ4RjlaTUtKdnpZdUN6ZEsyNEE3N0xLdG95NlVoMGhfd21RYUlmblAzMWUxdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiaeryA3aF7r&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saFpYSjVRVE5oUmpkeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5DaU1oUjVrZFljcjhwMjMzaGZ3dHNfTEUyVEUzT1F6WHlXSVJqaGlMNHdVQXpMVUoyby16RzFoOEtGUDZNeTVpQ01LeHRneXRSNVdXMUl1UDYydzhwZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txVazUJZzIiv</t>
@@ -496,7 +496,7 @@
     <t>fi9jjDawFbE5</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi9jjDawFbE5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNWFtcEVZWGRHWWtVMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5mcndvXzVMZ2gxc1RQaExXaFJCRGU0R3JXRDEtMHgtcFFaTXdYMzVvazh3YlREOTh1NnZhY3FyNnQzRVhUdDJFdkdSRHE0X3lZenB3TlNQMHY2Zl9XQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi9jjDawFbE5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNWFtcEVZWGRHWWtVMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC53VVA1TTlYWlB4eC1xdE9DckpEQXVTRGhINGRlaFlsNG9wajA4MGNzRExMTGU2TXozRHo0ZFdINF9tOEYzYXBuTHItR0hIZHRTWktxVzdUSkEzQ2xkQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txPsnZFWG26P</t>
@@ -505,7 +505,7 @@
     <t>fijFISadmHyW</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fijFISadmHyW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scVJrbFRZV1J0U0hsWElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC56NnFNMXc5X2hTTzF6VV9vR3prQnBuc1o0Q3JhU1cxVm5QaXlCZ1d3THV1X3B2Z2NoR0pRUUZvd0dpMXo0NzNSZjVuaDYxTmlua2lITWUzNE9FZWt1QQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fijFISadmHyW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scVJrbFRZV1J0U0hsWElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5MdjcwcFg0eENWMHlDNmkwNHdYbzI2Qmx3MzhXZTQxYUE0dmJON1RwajZOZTVqT05EOU5leVFoZGFyRkdicS1DQ3E5eC1GbVZqZzd2TjM3akFCb2xKUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txn5RKEI6wMJ</t>
@@ -514,7 +514,7 @@
     <t>fix55uPPbrwn</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fix55uPPbrwn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNE5UVjFVRkJpY25kdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5mejJIRjB5S3Z1dTh5SFAxR3JyUmU0RVVVb0hIUUgxNlFCVEdEcE16YkJzbThFaUlSRmdHMDdGYkM4QVpESFA2YXNaZ05DQ09POVhYQWNfajJWTFZPUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fix55uPPbrwn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNE5UVjFVRkJpY25kdUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5hVG5kdlYwaFhrbnJkWGRpRllkTG5QTE56dWw1YS1qN05jRVhYMWkyWjFvUFBJWkpqNlBUaW1NVGx6UkNqclI1Q21LOGpFU2lwaEx3N2V1dkt4YkNwZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txrScJw3ibcf</t>
@@ -523,7 +523,7 @@
     <t>fiSorqz1LeIw</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSorqz1LeIw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGIzSnhlakZNWlVsM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5pcWlfRjRjTG9ST291VlVBaE8zcVN4alJMdEhFOHBNVktBd1VNNm4zZGZad0Q0NHotdExDU01JZUlkUVZiQ1FVbXctTThVQjB1VC0zR1F4ZkdvLWNHQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSorqz1LeIw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGIzSnhlakZNWlVsM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5mLXVZYXpySmdXVTI3aThQdnRlVE5LZm1yQjZCUDQyaXdOeEhaaG05MndhOTBVcGFtZGYyc3J2ZklzQko4V0V0TkxqQ19fQjVkNncwM2dTLWpyNDNvZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txSCocezz1Fv</t>
@@ -532,7 +532,7 @@
     <t>fi2dlNS5xl56</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2dlNS5xl56&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVpHeE9VelY0YkRVMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5tWkFuVF9QTUVyRzZ3NU8wVDZrMjdMT2huRmdnWk5LM245ZzVYejFGdks1U2tURF9MUGJVb1N1eENSd3pWUmtoVmY3LXFYZWVibFVOUFhGZWNfR3RUZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2dlNS5xl56&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVpHeE9VelY0YkRVMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NbFU3UnU5NjdncTJ5TEhraE93cEh3NVpWLXNQWTViQ05WVWk4RFRvUzVuQ2tHeC02THVtWjJOTW02RXMtRmp0ZXFucDF3dTFuSURiaEpXYUtoRFEwdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txT9BTVwNs24</t>
@@ -541,7 +541,7 @@
     <t>fiUKBRvKyBFz</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiUKBRvKyBFz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVlMwSlNka3Q1UWtaNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5RUTZTZHRlTXlIcjZuc1BNYXdQQzNxWC1IYngxX0hCYXZLRE9VRjJyUUR1dXJ1aW5hcERNRGVqY0FsOWxZN3VjSHFYNWxBcFRKT2tXQUZlWVFPRG9RUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiUKBRvKyBFz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVlMwSlNka3Q1UWtaNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5YVFA5Z2hkVVhuWm5URWxfb1Rmay01Ny16Yk5mdkFmaFdqMFhYcUxVSkE3d2R1MV81UVBxdlpJZ2s0dXRxUUdZOEpwY2M2SlliaDloZU5vYnVLWlRQUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txtiTgYBPfEl</t>
@@ -550,7 +550,7 @@
     <t>fi615tCbw3L9</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi615tCbw3L9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMk1UVjBRMkozTTB3NUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC55MXM2OUh6UmJaX1ZDeEZMQTBpUjZVLS1UYkdRdzlXWlBnY1AyOVFCejJwdUhRNkV5NWpYWE5VZHBMZ2lVaDRFY0RoTzlvYTJaNzZkc05zNHhybVNhUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi615tCbw3L9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMk1UVjBRMkozTTB3NUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC40Q0l4Q3VBcmpnSS0wLWs1Y2JZTjM5RkxjUzRGNmdQdmp4MHJCTXIyelJrTDZERVJ6WEZJWkJFRGVvQ2F6TTdmcEsyNmJtSklJWUtsemMxOEpPQkRnUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txXrRXXaROM5</t>
@@ -562,7 +562,7 @@
     <t>lyft_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=firiB4wctvhy&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seWFVSTBkMk4wZG1oNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5LcUt5UURHbnktMjdvRllGZ19MMGVGdm1FLV81T0RPcTIxaVRMalRBc1QwZEU4bEFhQjJYRTZ1OTVhZ3dGUVJ0VURFQ21LajFwckhocWlWaFl0UklUdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=firiB4wctvhy&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seWFVSTBkMk4wZG1oNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC41a2VFVTRMSnlHaU51ZnZwRzVuNWVXRjgzRld4djhsdlZ3OURxUkpTc011NFVjVEIwazVUdFRIQlg3Vl85VFhRMHRQZjJqTzFlbGhwMW1GSDJxdHVGQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx1Wx6d1xOev</t>
@@ -571,7 +571,7 @@
     <t>finG9i0z7hXn</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=finG9i0z7hXn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdVJ6bHBNSG8zYUZodUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5lR1pDUDBjVU9jeUoyTS1xZXZKanpDWkx1Mkg1TUJyQVVQLTIzYmNGTmRLWWpaZDhPb1pObHlqdFJkREpDRUZkQXBXa3RVOXhJdDA5WTZiNnRqTmhxdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=finG9i0z7hXn&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdVJ6bHBNSG8zYUZodUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5GbDE2Nl91OFBMLVBJT01aTElkLVZmWkN6STNGSHNvY292QWFmdXE1Qi1zakRyNWlvM0pOV2J1elMtbEpaSnFhUlVxM1JVX1ZyZUNGSzZoSlZ0bm1VUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txIrDlzvnTLw</t>
@@ -583,7 +583,7 @@
     <t>marriott_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiK94c26JQbN&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTE9UUmpNalpLVVdKT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5XaWNKWjlkbloxSzVZRmVKVjBxZWxpczVrWWpxcUpDam5namxaOHo5SHJrMjJwalNqTnpnNHFDYmtoNVZBdFI1cnBESkx2NGdEaTFTSFhqeTIxOWswZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiK94c26JQbN&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTE9UUmpNalpLVVdKT0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5KNzJHd2NXclNIZGNzUVpIUzhrSjdMZTBmTFZLbEQ0NmxFVkxMTllEZnpEaExpNmFkOV90RzdKMnNERmhVVG1VTW1HbWhuYVd4S3YyRmVscEJiZzBBQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txeSOH7drnOK</t>
@@ -595,7 +595,7 @@
     <t>staples_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizWB2mOxAV7&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlYwSXliVTk0UVZZM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5fcE8tZ2J6RlloLUZTY2daR1lMaFFfUGNfZGtYWWZLT01mYjFjbGo1VnpRVGlXZ3J0S1ZFTDJwLU9DQ0VkbHVVQVVBaWdtaURIaWE2eEsyYkkyamtXUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizWB2mOxAV7&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlYwSXliVTk0UVZZM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56bXhrVjlNSm5kYm1YamFQMUc5THBjNTU3NkJfWDZBYWx3NGs2YWZJN0hIakw1QllEeElQQWpwa19FeDBrYmxORTRNVzU0MnZTTmYtZm5hd1pnVmloUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txqD1ejVRxVS</t>
@@ -607,7 +607,7 @@
     <t>dominos_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6RjIB6h48w&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlVtcEpRalpvTkRoM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5QTzMwMmswXzJrd0ZhV0tBNkVKaEZhOXh5VS1CcTNhQlRUemhwRVNtZHBZRTJCTzJac2I3WnBpNVJjMFJlX2Y3MGp3b3ZwNXlOVkRXZlhJYjl3TUVvZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6RjIB6h48w&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMlVtcEpRalpvTkRoM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4tbFA5dGoxQ0N2NXZpdGlwYmtHRUQ3MXZGSnFMR0YtdVdLXzE5UjhfN3RXM09QRmhFeDh3T0ZwQVdEMTlEY3FMLXU5WV8tb1JKNmRzNWE4U1h4Zl9oUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txHNoviHEPBz</t>
@@ -616,7 +616,7 @@
     <t>fiNixQOtgIB5</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNixQOtgIB5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT2FYaFJUM1JuU1VJMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5vd1FFdVNTTnVCbFhiMDB4YzJaVV9yZWthLTlPUkg3RjU5RlpqZTVyanBqclZMRnRFYlJ5S0xWNGpXSG9OWjFKajJ2Y1hfUTNGcGdrLWRMdVNyNjdHUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNixQOtgIB5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT2FYaFJUM1JuU1VJMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5LNkJ5eTJ5SUM2QXNtME9TdVpfUkNYN3VRZnVaOUpuMy0yNnowa0xFcW5SX0dDOGxOd19MWGl3dlcxWU1uYTFkTmJKZjNtMlFrSlhvM2RXaXBoNmFMUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txqhkvFBiP9E</t>
@@ -625,7 +625,7 @@
     <t>fiCMXsRU0Mqw</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiCMXsRU0Mqw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRFRWaHpVbFV3VFhGM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5lNzJkbHI2NUVvNTU0bHQ3SWFQUHV3Z1Zpc3RvdU9PVHNRTmtudThGRDlyLWgwQ1VRRVhQbzFtbGMwa0o0bld3X2E3dHhVSzk2ZDhhZHJLdlJKVC1qZw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiCMXsRU0Mqw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRFRWaHpVbFV3VFhGM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5tRTNRWjZuVXA1MHFVZmZKbXNKclVLY3BhRnhuUEFYcTFJanlmeEZacU9ITTJpaGNXemE3YndfVjhsSjR5U1V3QlR5N2w0SGh2S2JVVmp5djFBYzU1Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txW7FodmOytz</t>
@@ -634,7 +634,7 @@
     <t>fiQN6pO9Efs0</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiQN6pO9Efs0&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUlRqWndUemxGWm5Nd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC54RTJTOEJoSExRZW1XT3BwVHpJRTJJNXNwYk5sWjBEVmRSN3FTX2RFOWFDV3hLMklnY1VOeWdvTXMtNkhfTjl4VWNlcVBkR3kwMVQ3Q3NON2M4YjY3Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiQN6pO9Efs0&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUlRqWndUemxGWm5Nd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC40dHN0M20zcGx4cWJkMHViREVTNEZ0dWZCYndBaktQTndFbHhCaTgxT1htbXJ3Y3VrZVdfbWQxb05XVE5SZjk1aTA4WElYN25PVjd0dGhFdDlxalVJdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txCteb2e78g3</t>
@@ -643,7 +643,7 @@
     <t>fiOjyNGKAXbF</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiOjyNGKAXbF&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUGFubE9SMHRCV0dKR0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5PT3hHYzNZRC1WVS1SZWs0Q1hiRENQWEpqRUxST2JudllWNjhodWJQWkZJakJRaFRYcEdtOUNpZzEyaVBYV0ZCYW9tNG85TFpNY1Fic1lnQkIzM0wxQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiOjyNGKAXbF&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUGFubE9SMHRCV0dKR0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5QTldNOWFuYXUtdU5SU0FSUXp5aUhIcjNWdFd3YjRfNTJENVpGd1hFSXlUWE5fdEdxMXlOSFpfV3F3bG9WWld1SkM4a1lCV0U3N0FpVHlKbElTOWtGQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txmyy8Zv9G1d</t>
@@ -655,7 +655,7 @@
     <t>uber_Nov_10_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5F5ceMzIfh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVJqVmpaVTE2U1dab0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC55WnBUTW1ORDVJalpZbEUzM0lWd1daTnhpejJRWFNkbFBpd3FYU09MbEEyek9aX3BTVEhkanFZU2tlbVZVSzB6T2xLQmdxc0lkcWxUSWlRaFR5ZHRzdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5F5ceMzIfh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVJqVmpaVTE2U1dab0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NS095NEFDazE5Wlc5ejR4Z3pEX1B1c1F5S3NRMDVYV0J6LVNnMmUzblNVc1pvdnc3VUJ5ek5yYWQwY09wZ1MwX3ZLOGpBazNVM1BBREVYS2VIUEZKZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txm9Stk7uIjy</t>
@@ -664,7 +664,7 @@
     <t>fiPuLpt5uzt7</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPuLpt5uzt7&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUWRVeHdkRFYxZW5RM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5tTXVPNzMzQjhnQUI4VktCSExHbzc5TlZWMVAwTGhkc3BhTkZCM29SdWE3UVlDMjl6YnBuVU4xaUtkRjg1REVVTGVfaGdaNnhkc0ZRaW1ZSW1ReFdwdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPuLpt5uzt7&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUWRVeHdkRFYxZW5RM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5XbVBrME0xM2dPa3ZiUVc5aDJ0eVJvR3NiVWNPRmpJTzNyZjFSTlpoYS10ZXNTam54SjhQemxUTjhPaXZsY291YThWb0VoQUFHMlgyOXdyQTBMeWNCZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txIouVv6onY1</t>
@@ -673,7 +673,7 @@
     <t>fiy7ZInVxmBq</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiy7ZInVxmBq&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNU4xcEpibFo0YlVKeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5WbGRNU1ZPdW9EaHBTWEpyMndqSkl0ZU9HVWRtQTFSWVZHWHp6R3I0T1MwbWdfVUZhaE1VRERSYjVVVlAtLXdkUy1PNU1hNldwWExUU1o4VDJXa0VtQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiy7ZInVxmBq&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNU4xcEpibFo0YlVKeElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5aMExhb2dtNUN3amxvbHdWN2dFM29mQWtKX3ZrQWdTd3Q1N1l1SDRzVEY5VThEOFd1R1N2S2VJM08wS3lPLVNtb0swQXdJLUZXb29SaHBjNEFfWDdVdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txoi8Mg7Mz8j</t>
@@ -685,7 +685,7 @@
     <t>amazon_Oct_16_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitA2i7cS0lV&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMFFUSnBOMk5UTUd4V0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5Ra2t4Ujl4Y3hYRVZLT3MyU3E3clgtai1YaE4xcUk2YnFiSnZ4T0J5SldMUVBiSDFMV1NfMks4MUpIcDVRTnRMc040RDJFNmxtN0wtUWZTY3c3aXk3Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitA2i7cS0lV&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMFFUSnBOMk5UTUd4V0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Ka3czc3hxN0o4eTBXTHlFc2czM0l6VTl5Mzk1YkpnVU1CVTlJcVM4dVd3RUpFdjhqa25MYVdvcWdLYVdoc1JYSWduUEpWbXVoOUpTNkVHYjExaVhWdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx46izSwgkHR</t>
@@ -694,7 +694,7 @@
     <t>fi9WoJ5y8PLA</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi9WoJ5y8PLA&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNVYyOUtOWGs0VUV4Qklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5RdDRGZHEtb1JGZmEzeG83YklHV09yMVVJZ3RDU1NlbjBjaHpNYzJvc1VuVHZPZnpNdElLamRlRFlQeE52LTIyVmwxZ3lFQkRjWGcxTklaRGtnWjVHQQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi9WoJ5y8PLA&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNVYyOUtOWGs0VUV4Qklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5FYTZsSGZZb0hQQlFSZWdwMFJzRzF5MWhiM2plaUszMDYxbGp0VE5fR05CSmo0OFFNU2RHRFQ3N0RlN3dNa1QzVkRkTll0VmVKSFo3X2FocDR1NWI5UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiCyQaoiOSdv</t>
@@ -703,7 +703,7 @@
     <t>taco_1129603102000008_385c4c5d93df4f70a4c58aedc8263852.pdf</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiCyQaoiOSdv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRGVWRmhiMmxQVTJSMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC51UFJ2MWpDQTg5cXpjalhWd18zeUo0OXN1OExQU29OQlJRazIwUmRzZzM5N2k0djR5ZWtpR2dHWk5yOWx6VmhzWEI5RVFjcGR1UUY0ZDBGSi1SY2N0UQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiCyQaoiOSdv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRGVWRmhiMmxQVTJSMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5McVpwaFhxQ3VPaFJEOW9LUnZnVHFwU3hHMEFsSVNiSklDSzFRU05yZExMd2psdFBsTUp3cFVaTmVsRG4zc1FreFU0NF9ReHJxTVBqczYyR1MydWhWQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txmlkA06dpqt</t>
@@ -715,7 +715,7 @@
     <t>marriott_Oct_16_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiRIaAh1kPiC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sU1NXRkJhREZyVUdsRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5KRkVvanpVUzJxM3ZoMjVGNmpacktfTWxkc3R6Vm01YVNJU2ZTYlBhQWU5WEJENU5YT21wQjlITHhfM3UyQmJ3SkN1WHNtUE1DVHNDaFdZMnpXOWN6Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiRIaAh1kPiC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sU1NXRkJhREZyVUdsRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4xOTRTN3lUZHRyaUF6ZmFGbEtxNXVjS2xjTGE1a3luTGpMNmFTdkRnTzlDWnRZcXlFYUZ2MGVrUTg1R3UzbzlMNGppcjNJMEhfcjN2WGs2ZjZja2wyUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx2tlH0ajgZP</t>
@@ -727,7 +727,7 @@
     <t>lyft_Oct_16_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiOiQUF27p5l&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUGFWRlZSakkzY0RWc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5fb2JuY0RhdU5HdExrNE1DMTRES2ZZSHlJUnRyY25kLU9rXzl0elliLW8tb1pyUzhma0NYQWM5NkJUODk4R2dLbjdjVWFIaDFZMXg0SWkwMkJ4dzRBUQ%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiOiQUF27p5l&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUGFWRlZSakkzY0RWc0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5nUU9QdC1lcGJIcHdtbElDS2ZmVVNPbWpNcFd3dG0wdGZ5UzNUd3p4ZnZZR3RkRHA2Um9McVhNanB2ODNOWi1STTFHbS01MkZZbFJMVWZaeW9KaUc3UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txvSt5sr6fvR</t>
@@ -739,7 +739,7 @@
     <t>lyft_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fim6PRFrekPp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdE5sQlNSbkpsYTFCd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5YMzhwelVhekU0Y1VBdWQ1TDBFaU5OSjZpQVpxRTYtZmw1eUY1eHNmYmUwbEEwRjJTWjJkM05PWTl2V0VtcWhYUnkxX0xlQWpWSkQ4c04xQmZsWE4zdw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fim6PRFrekPp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdE5sQlNSbkpsYTFCd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4tQXBDMWdhNGdONmUzajRHUXdvTmdQVHJOb2ROQmRaby1LMTdUazdoaU9PeV96VU8tOWdqenpQM2NadmdDS0RtMjBoSkJYVUFGeUthRHp5RkZDQ0ZuZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txbe97B3fs3Q</t>
@@ -751,7 +751,7 @@
     <t>dominos_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2Qusx8JdTQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVVYVnplRGhLWkZSUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056SXNJbWxoZENJNk1UYzNNVGcxTVRjM01uMC5PR2FFajlnbXFhSkp1SG5iaXo1RG5FcmpsLVZkQk1qUmFPYXBMTGwzZlU0Z1RKLXVmeDVGeE5QZ2Z5WUk2d0huTFNFZlJONE9wQ2M2WDlNb3lGUnN3Zw%3D%3D&amp;X-Fyle-Issued-At=1771851772&amp;X-Fyle-Expires-At=1773147772</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi2Qusx8JdTQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1reVVYVnplRGhLWkZSUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5WMlB6SzE0dERUUVJGLVlVMGt2OUltRHIybVlTS3BpMUZzOHBhekNIQ0l1SE1tWU92cmpMU2FQZURNQ1p3VkM0SlFlOVE2UDBVZ1U0RkJJX3ZQWlFwdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txCLGhMKyEbA</t>
@@ -763,13 +763,7 @@
     <t>staples_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiLQEebief0F&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTVVVVmxZbWxsWmpCR0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5CaUNNLTcxTnFqdkExMnB3ZU42V2JiN3BSS2pyUGZrTEJfeFpIa1NnSFJCRzBpUG54ZFhzNUtNYllMbE8yYTF0cmVXUFlSRmdXdXRINEI0RFhNTmVxQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
-  </si>
-  <si>
-    <t>1771851773</t>
-  </si>
-  <si>
-    <t>1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiLQEebief0F&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTVVVVmxZbWxsWmpCR0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5oS18zMF93TTdBMTBLZXZHRFhVVTIwaVdnUHMtNW9fSWxiZ1JZSlBYNmhSUk5OOG5NNy1UcnFsVERwWWdSalBtNUVOb2p3Sk1jZVB2UDJVaXFSTTRXdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txcb9aEXBuiO</t>
@@ -781,7 +775,7 @@
     <t>marriott_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiI7w07rHhdQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSk4zY3dOM0pJYUdSUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4zb1pZZFRIOW5wemx2TFc2ZWZEWU14ZnBVTlFhZ2R3bHRMV052c2I4TXBNM1JSbVRTRFczOUk3SWE3SHZUZTNZWUtHb0ZEckgyZXM0N0VHcnU1SHpSdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiI7w07rHhdQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSk4zY3dOM0pJYUdSUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4xOEdSU2JxZ1BXWmRQS3NlVDNzSFJNZlZXWVpha2wtOEFKNVZuNDJ0UXB6bU1GcmpjTTJ4LVNySXVFcGtEMXlqeTZrWFRaQllkN3FFTkhZd2I3N2RaQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx0z9PP5cWgh</t>
@@ -793,7 +787,7 @@
     <t>amazon_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi8PG2xL3iJh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNFVFY3llRXd6YVVwb0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5YUnBWQUI0LVNIMEI4bXhZeXVrc1B1NGxLUVRVX2JzN3M4TUliVWJ5d0pMMHM0TEJpWXBBOURSaHpONVdZT25peUJpcGtKWS1ibndlRUstclZJbVJmZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi8PG2xL3iJh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNFVFY3llRXd6YVVwb0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CMFRISGdKemlPUXNWbnNmYXZOMTdkaFdiVldHTkI3bjE1UWtLRGhYdzJKVElrZ241RllfalhZN1V5Wi1CRG9RYzg2SzhVQmpHc1Y3OFgzQVcwLWRlUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txZ08dRNdQ8L</t>
@@ -802,7 +796,7 @@
     <t>fiASLySWvwtM</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiASLySWvwtM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQlUweDVVMWQyZDNSTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5fX2NCTUl2c0tMbC1mZ1liYU9TNUcybU5pdDFGTi1mSTRTQ2V0MXFwOTNOWFF0OG14bnpyaGU0LV9DR2g5d0VQdldlcEt4RjZmcXZ0LW82QW5EaW9UUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiASLySWvwtM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sQlUweDVVMWQyZDNSTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5ZNGRiNkxOdE1YeFFrc0toNGlrVUpQOWJ3Xy1IR2dyTW9LNFRyTWVvaFVsWWg0ZVlsbXhDUklTYnUzZnBvNER2VGNuenZMS2h2OXcyT0lTYmlYem83dw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiecdKfB6DXB</t>
@@ -811,7 +805,7 @@
     <t>taco_0746184071500003_ba35fe3e16b34a928f7e3bcec6cd6cdc.pdf</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiecdKfB6DXB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFkyUkxaa0kyUkZoQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5GRjIwWVVkRjcydkx3VURWQWJ2eXM1aG1IWl9JdXRaOFlVYk44U2dDUWtaR1J1Y1BLY0xoZjNXR0FhTWd4TVhVeGowcTNJcGM5LVNOYl9maW55M0JVQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiecdKfB6DXB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFkyUkxaa0kyUkZoQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5aY251SHQ0LXRQQ290WU1QU3lQMnUzZXc4bWRGSHE3YkNvUFlHVnk3VnUzSG5kYjFsdjlvbGlIUkE0aGJvbGpET3B1WkpfcG4zVlBoZm4zX29xRE93dw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txQnaXCFnMW3</t>
@@ -820,13 +814,13 @@
     <t>fi5wIE61mvKg</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5wIE61mvKg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMWQwbEZOakZ0ZGt0bklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5wTzR0WjlRVDZuajE4XzkxTUVjSzFWUW5UaXhid2ZSZ1U0OHZ0S2RLY05ZYV9BY1dpYzBXMndWMG8xMFJlREk3Vm9YdldzekV2dFBJMGJKRlQyanlLQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5wIE61mvKg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMWQwbEZOakZ0ZGt0bklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56UVcxeTJLLU1LdHQ2RmZPZFUtdld5Y3otTVV6NGduOTdxZ1NKLWZEbm1lQlRQcXJvbk5XVHpDNXBQNDB3a0MxNTYxLTUxeFhWeUljUE4tS21Ic3JkZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiRSZxf9wGlL</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiRSZxf9wGlL&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sU1UxcDRaamwzUjJ4TUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5NLVdwUGxPWC05TXFDVE5DcGJTTWdtZU16b2FNOG5WeHlFX3BrdnRrOEsxeDBDRVZmVGxFRDhaU0FIdVNoZUhTNlAyOFdpNTQtTVhaM1E5Z09QTUw0QQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiRSZxf9wGlL&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sU1UxcDRaamwzUjJ4TUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5EdmhYNnF1UmlsX2RVa0ZDbHd5RmEtc19yeHhISTBoTUxET3VGbklGMWthTkhxRURMWWlYSDJWUkQwWXI5cVUzam5YTTQxakVsczZMd3dNWHBBRFBmUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txog3JWCg6Q7</t>
@@ -835,13 +829,13 @@
     <t>fi5Qhzeh3DGQ</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5Qhzeh3DGQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVVXaDZaV2d6UkVkUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5KWTRacVRnRkMycWdIaFQxaFdYNVBNZDhZTHVTQUd0ekpJbFFMV0R1eTJOSUtuMkQ0VzBNaW9JM2xHUUtjTUpHcm56ZkhINURsXy1DUjROaklmYkdLZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi5Qhzeh3DGQ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMVVXaDZaV2d6UkVkUklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Ga2JvVlV2dXRNZUdlM3VHSWZjd25JckxFRTBqdFNXTXV3T0Fla3ptV2M2WHBJSVM1RV9JOW9mYXB4aUlwdVh4SEVxZDI2VElydE14YXI3MS1HQTJsdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiGpcmN8H2oU</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiGpcmN8H2oU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSGNHTnRUamhJTW05Vklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5GN3E0dnBtdWVNRXA1YW1Nbzg2Uy1RUXJaRXFkV2dUTEdpb1BBTkowVEhmRHZWTmJ6dUQ0SmQ4SnBMT3ZDNjIzUzRqbV9IM1pKYUhmUmRTcWRDblp0Zw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiGpcmN8H2oU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSGNHTnRUamhJTW05Vklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5wa2dCUm5jcks4ZUp0RGV3alBrRWNwbDNFazY2S2ljY1M1X045NzdnVXJZUlRpOHZmdVppSTM5UTVXNXN3SUFFY0h5SEp1WFFPa3Framt6TVY3aGprZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txjyMsaImNZA</t>
@@ -853,7 +847,7 @@
     <t>uber_Aug_06_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNfPRQBqsAg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT1psQlNVVUp4YzBGbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5hWXMzbzdFdXJvamZpcm5KaDZrbjJYcmpNY2NuajA2QXNzWHpzRU5vRXctYmJzOU8tWFZUMy1neV93QTNhR3dkSzE5by1yY24xTFNib2dNWTRmckcwQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNfPRQBqsAg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT1psQlNVVUp4YzBGbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CWHotRkN1Q19DdWxPS0xaeFhpRmZDTzlkdmFpTFpfdXhtSGsybkpnMUZtSW82UU90aTgzQnRtTFlSVWxubEVHZmhGV1RUQTJlWW9OSkN3Vzl5TktuZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx5RT33XNf1V</t>
@@ -862,13 +856,13 @@
     <t>fiL58DDuXl1o</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiL58DDuXl1o&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTU5UaEVSSFZZYkRGdklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5GanpZZzdabzM4bUZwNmpGZi1Qc3ZWRFdlT2RiODhXVGNhUTJWWXJQdkozRWdKdXE0SUIyWXlTSnZPdmlaS0VVWno2ZDV6eTlFY1RYV3B3RDM0VDJTUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiL58DDuXl1o&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTU5UaEVSSFZZYkRGdklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5VYVpsYmNrWUE0MVBLdXkwMW8tMXVOSDNndllVN0o1REFkdUFIa1gwb3Jxa3ROMGo1Y2JLR0hhQmV0b0pCRHlEeGZWX2xUWlpFTnBFQV9velhaRzB0UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiMmdBytaOLx</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiMmdBytaOLx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTmJXUkNlWFJoVDB4NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5SVU9ISXEzLXJYRE5zZDdUdjRHdjdXRm1qVk9iRDBRSVRlay0xQmVkbTdsY1lpclVtODJXa3d4VnZvZGtnSm9CZTZIY2RoUldxakZxcWtFa3ljNXRCQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiMmdBytaOLx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTmJXUkNlWFJoVDB4NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5yaWgxcXozZ3pWQS05ZXVHSTAzTVVqUTNUZFZfT0VvalBFc2xJTXNNSm9GdnNTejZnZk1uQndwcXVCemhqek4wbUNPbG4tQW1Ld0V4WnNJUk1SRFdwQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txxcFzvFuMOv</t>
@@ -880,7 +874,7 @@
     <t>dominos_Oct_16_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiYgf7ywBtxC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWloyWTNlWGRDZEhoRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ndldRRnFMUTQzdVhZcU9JUzNYcjM3cEotY0NOQXNPaWxIcEdHWnI1Q1BuTExwMzBSa1oxXzRLZlBsU1NNM0hJU0hrLU5mQjhEd25LYmhQV3RNclpNUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiYgf7ywBtxC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWloyWTNlWGRDZEhoRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NLVQwRVF3dmNnX3R4cm8xby1jUW5wZXdpYXlVOXR2QkxsNjNXYW1kTGkwSTNqU3JWdW1KbXh6VkZrNjNtdXQyNWN6dTVnX0lEOU1QdzFPaWU2TVpIUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txk9etpUKzWn</t>
@@ -892,7 +886,7 @@
     <t>staples_Oct_16_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZnDSysU1Lu&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWJrUlRlWE5WTVV4MUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5CV2lHTkdsQXJkUHV6dVVIeFZQTWdpUzgwakNBdVVoeHZHcm00RmFpU2JSTklBLXpmNmVaY3d3X0FHM3dPS1ZhRTlTOXFlVmIwTlJnMURPUWNhU1lHZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZnDSysU1Lu&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWJrUlRlWE5WTVV4MUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Eaks2eHYwME83N3RaTWwxeURJLWZTYUU4dy1OREhZN3FrWExZRHFzSzl4a05nb00yUW1xYlp0bXBmV2w0WHh0cXBoWF9GRnY5bFZ3V3ZnSEtVU1JKdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txAMT2MCUHWI</t>
@@ -904,13 +898,13 @@
     <t>taco_1093548072900006_cbe5e981fe334d45a639d1f449fbc500.pdf</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZp4ZEtgZKl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWNEUmFSWFJuV2t0c0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ScmNETlpHdnkyRGQ0Rm5oamxKQUUyV1lrRFVBYUQ3ZXBMa2VIQ1F1dUlndHZaR01IRno1ZjhDbFB2UDZNa1ItX294R2hMNTNEY0ViMWVNd01sbHZYQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZp4ZEtgZKl&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWNEUmFSWFJuV2t0c0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5kWWw1dVFrYU92cVRtUGI4cHNLR1p2SjcxbDlINE9WZE54YTVtUTc0OTRmalBCVWN2OUZMS0puR3gwaUt1MmxreEFHaU5mdEdfQ2RoRlRwbEppcnFJQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fiZwFY2jcbiY</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZwFY2jcbiY&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWQwWlpNbXBqWW1sWklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC56Z19na1ZJOFRBNlE2dUZMd0I3Zkk2MW8yb3I5aXZsLVo3RWJxUDA4N2ExR2xMUXl3SE1ZVUNRM0NTdGhRQjNyNVlKc2R2S3VIbHpjak9zbVF1N2Jhdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZwFY2jcbiY&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYWQwWlpNbXBqWW1sWklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC51Nm9ZXy1EMGVGc3liUGM5X3IyQ1BXNnZvM1VKLWlQU3ZvX042S1FseHg5eTJMdHVRX1VFZlhXdlRFMEZrQzlQX0NFVGhoVXViSnFqUGVQa0pWRlVKQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txaxjWxVz2WK</t>
@@ -919,7 +913,7 @@
     <t>fi46pXDSrC7a</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi46pXDSrC7a&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rME5uQllSRk55UXpkaElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5SdHZsb3NRc1FOc3JTQzZkNXlhbFZVUnhOR3BQU1g0RmJqcGxnUGk5dzlSekhTM2dvRElIeUVVRXZraVg5bW5qQTBoNmxRVXlUenFobTRwNFlscjFjdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi46pXDSrC7a&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rME5uQllSRk55UXpkaElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5TcXh3UEF0VlViX2M0VW9wcUM3YjJEVDZFWDRYVHhNdkxkN2ltc2Nibm1PMmJiZnFxTHc2cFhtY25DbnZXeFBCN1JqTjljS1o5QWIyaGRzVlVwU3BJUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txIVLK6uWl8N</t>
@@ -928,7 +922,7 @@
     <t>fiWXhbPbgRCB</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWXhbPbgRCB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFdHaGlVR0puVWtOQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5BdWFHM1htUFFFbXlTVG1GS1pwb2Nab2VKdDQzUE1aanBQbi1ZY3FiSlRBLVhWYVQxT2xJN3IwaFdiTkxiV0JIRE5yRnZrbEF6dlB3c3N0MFoydExjdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWXhbPbgRCB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFdHaGlVR0puVWtOQ0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5iLXg5WWZudDhsT0NUTS1XRW9YRUFiN3FqUGpZNjRHQUR2SEx2WkptT1dBVFhTZmQ4QnJmZGZyQ21tOXBYN3hmRmhwUmhCQ3NaMEtfYTVXTzNhWWpRZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txU5DtG58Tj0</t>
@@ -937,7 +931,7 @@
     <t>fin0YOvrZItg</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fin0YOvrZItg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdU1GbFBkbkphU1hSbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5obkV2T24yb2FtWkNORjZfSFM0UlpMcnV2aDdmbHZINGdaRnJ6Y1hzbDNpUzNYMzdSenFyWGU2RGJ2MGl4ZjRmaTdyeTg2OVhrcDBNVU1iWWhMV0dPQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fin0YOvrZItg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdU1GbFBkbkphU1hSbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CNTZMeEoyRTdWZm93Qi1vbEdjemRMQ21lcjZLVmItWDVoM0d1ZmxnWGg5UTJjOGNfajNmU2g3a2Y4NEVMYXRDUjlaU0xTeE1WTWN5NjQ2UWs2b0tndw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txYVY53lBsa4</t>
@@ -952,7 +946,7 @@
     <t>image/jpeg</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizDpDRFDs6P&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlJIQkVVa1pFY3paUUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4tdGtWb2M0MDI1eml6SU55VUZOOThzcm5ra19MaHAtYmFxc1gxcUI3aUdUVE8zZWMwT2VmUHViZjFCUmdVbGVzM1BoT0ZDR0ViZEpuSm9icVpnUnVVQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizDpDRFDs6P&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNlJIQkVVa1pFY3paUUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC40MHNrWFEyLVBNdFdXY0p5LWtpMU40bldTb1FaRk53QWNlVno1b3ZjNmFQSEVaUmd2ZWNFc1dVd2gxSWE5YVlZQlJuU3QxZ1hnUXF0c1lWUWc0cTkydw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txrg0qE3bYJF</t>
@@ -964,7 +958,7 @@
     <t>amazon_Jun_27_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiogBJSJVr14&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdlowSktVMHBXY2pFMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC55V0N4S1VKdW12S2N3N3plZkhsVm4tT0ZDYVhwREx1ZFYycEdIa1JuTW9oQ2xZSnZzQVpFbEo1VUJ0NUIxSWhKV1NCYnBocl9NMGtETm9EQlQ4b1VIQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiogBJSJVr14&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdlowSktVMHBXY2pFMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Vd1M3cDYtZmFseWJjNTJIendoX0dhdzlrX050MTg2WHZxNG9UZVZCWUVZVTl2MGllRllNenJCYVZ3dUh5dmhBUGRSR1E0ZUFDRWNHTDJuTW5rLVU4dw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txyv8BrQDtwq</t>
@@ -976,7 +970,7 @@
     <t>lyft_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fixOAS77dwY5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNFQwRlROemRrZDFrMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5JLW1xbWh5ZXV2bkJtbFdBdGh5U1Mtb3ZRZDRDZUZvRGJ0WGxaa0ZEb3dJYjRocFRqclQwWm9TS2ZrNDB2QWV5c21KcDk1VnVEZm9uNThwZTRNZWJldw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fixOAS77dwY5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNFQwRlROemRrZDFrMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Hdl9IdERiUUNJRXVUUFJKcXh3a3JTY1hsd0xoT2NlSkF6OVNETkFlRmF3dWJubUl2VWx1X3lsWmVIVl9LUmt4dGRIdkdORHFiYVpGUVRnVm9weU9udw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txX1mijD0Nuv</t>
@@ -988,7 +982,7 @@
     <t>marriott_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiwVKpv6hLzr&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sM1ZrdHdkalpvVEhweUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5VcUZCUElXMzNTM3F4Tnh6X2pfTzN0N0tJR0tjQ0dMUUlBWFFuUW5VT0FaN1FEUy1WQzk0c25LZWpTa3ZMZ2JKWnBtZWRBbHVxNGtPZnVKZldkUXVTdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiwVKpv6hLzr&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sM1ZrdHdkalpvVEhweUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC50SXk3cVlRZVJHaVBxbi00X3p0Wl9oNDEzWXNVX1JBbldycHk4T0E1ZndYZXBWNmZHZXQxcUwzbGFxdnN5N2xtMWdYaDlXczVydms0eGtYYlVrYkx3Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txujakKrZwGM</t>
@@ -997,7 +991,7 @@
     <t>fipEA65aRSQC</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipEA65aRSQC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1JVRTJOV0ZTVTFGRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5QenlrWTNJbmFTaGpQUHJFd1BlWkhja0dFaVdMNUYyazVHYjVqcUg5T0JlTGg4V2ZXV25FU09sUUNxRU1PR1BrMVJTTHo2VmNxUk5FWGd2RmxwV3pOZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipEA65aRSQC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1JVRTJOV0ZTVTFGRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5SOXoxNk0wVmY4bTJ3Nmw1Yjc4Und0T3hJZmdkNnBZbEJTcTRMMVJrRzhOcGhKNUUyNDVhaHV6WUdXbG1fWTFwN3dBcVVXdWtwQ2N5QmloVEd6b3RrZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx7kKlrSscDr</t>
@@ -1009,7 +1003,7 @@
     <t>dominos_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioze146xGrm&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmVtVXhORFo0UjNKdElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5NVm1iZ2NxS1VpejJkQlNnUnl3MFBVamxOU0phUnFkSHVhUlA0WXpYVTVCSTlxMnNtZjk4MDh0QkhCSXNUdk9qR1JSbDdiX3RVMkhndGJUR3lfaDRRZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fioze146xGrm&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdmVtVXhORFo0UjNKdElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4xeFRaVEgyTFFDdlRtQktYd3ZDdUNZZGk4SXlhQlk0QS1kbEVCU3pMSjRrMzl4WmdlZGxVaEZHMHJybUgydzB3S1IzbXZoSXI3U2ZJeHFpMGIzcDk3UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txPWOYZKljIJ</t>
@@ -1018,7 +1012,7 @@
     <t>fiyWOY4Sr8yw</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiyWOY4Sr8yw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNVYwOVpORk55T0hsM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5hSTI1M1VOYm9aTzFFZ3VlbmJmN2RFVlR6NkZLMFREd1Y2T0s3WG9YMmNfMVNYcTAtWnp6N1dsOC00eTZxa3dTYTdQR0VUM0tGeDJHTTRlSmNSMEc1dw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiyWOY4Sr8yw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNVYwOVpORk55T0hsM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5sOXlheHhiY3lsR3p4R3pFcWdCZDNqTjJuQ1NWRU1TNHdVUEo2LWdmSjVhOXdCT05RQVZ6UkpiSXFWNS1mRDJzamxKaHNyZ1dSSm5kUEEyWkRfejVYQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txD5RYLoCqOu</t>
@@ -1030,7 +1024,7 @@
     <t>marriott_Jun_27_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fie7uIFArcUK&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbE4zVkpSa0Z5WTFWTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5DWFNYRE9oV0JTSXhianM3eXItbGdqdlplZmZIcUJPMnp0OXYtOVZPV0oyWXdheFdrT052cGYxOEROOGhYcEVJOHBDZklIQ0RqcDhGajlSTmhPdzEyUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fie7uIFArcUK&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbE4zVkpSa0Z5WTFWTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC50TUhma3d4ZDNldzNaamwzUjh4TklIaEQ4QTh3ZGxYSWRnSkk2NWIwRUgyZk1fWThJMXc2SllxRlZyUUFiZG5WbmlURlBMemI3OTdwZXk5c29nRGF3UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txT7ueu8iase</t>
@@ -1039,7 +1033,7 @@
     <t>fidIf0Ju7WmT</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fidIf0Ju7WmT&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sa1NXWXdTblUzVjIxVUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5FMmpvYXJ3X3duOG5zU2V2cFJFbGFRLVh6RWNrX1ZVN01iZHpxRVZNSEZ2bjVVNmVUVXVONC00SnNOOHBpNmJESExYTzBGejFzQVRnQXVIWS1xU2k2dw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fidIf0Ju7WmT&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sa1NXWXdTblUzVjIxVUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5sQldKWWhLVDhfam9xX3BpYmlkS09XZGFSVTRST25RV0c4S2EwT1FpWmRsckpXSW5HU2xRZ1NWR2phdi1CeXFCdW16ZFJ6WDlyUkE1LTdVVnRBV0RJUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txjioK8XeFyH</t>
@@ -1051,7 +1045,7 @@
     <t>staples_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fixweACrIfXM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNGQyVkJRM0pKWmxoTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC44RTRuSzA4RTNjQ3U5WXo3TGNaLUpFZDFtN3pqTU9MeTVGS2VqR3g3TS1PcXRVUzhnRWlKUWRsLVVwQWZSX3U2UVlET0dOWjVOYmtrSHNIbVdJcW9Qdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fixweACrIfXM&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNGQyVkJRM0pKWmxoTklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5PNFdkMlV1MmpmSS1IUWJXemJFVk1DQ1BfeTFZQlUyanotMEpiM2I2aUI2OVREZ2xMczN6VUNjUVFTNDlZaHR4VGNtSWVfQzdTY2hFS3YyZ3Vnd2otdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txBGbKVixx78</t>
@@ -1063,7 +1057,7 @@
     <t>uber_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fio3MOSJR0KS&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdk0wMVBVMHBTTUV0VElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC52ZEg0amFNRmVTMF9qNF84aWkxY3dmUnJxZVJmeTZ6N1M4akVYajlWVkMzNWRadzFMMERxcnI2aXFpVGd4MnZmZTNnYUpmMUlFQkhUTEU5NVh0cndKUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fio3MOSJR0KS&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sdk0wMVBVMHBTTUV0VElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5FeW10RW5CWENkNUVrLU5rWVFvOFByeGJaYUtkcURITXlTa1ZqVUlmUTdkVzlwcU1TUzlsSFpaM1Y0V05sXzJQZFlSamtfOHNsOWlUVWZ6MkdoT0lKUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txeRuNEea98D</t>
@@ -1075,7 +1069,7 @@
     <t>amazon_May_08_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiErxfUJXJ4K&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRmNuaG1WVXBZU2pSTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4wZmJnUTk3dVQ3RXpIZWJnZXNjRTdZMm1pMk96LWNiZEp1eThmbFJvUTMwcng3bHpCRXczb3l2ck9QMlhhQmowS0pSQVZ3V2NkUHdmckotcThQY3lKQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiErxfUJXJ4K&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRmNuaG1WVXBZU2pSTElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5tbkJMemZIc083RHhMT3NyTVBHeDhYcEt0V1hkTFV6MjNveVQxcG1TOFZlNjNQNVAxa0RsRjFiVk5ZejJqZlgxTklRd0p3WVpKVWVTY1FiX0dGcVJ5UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txx4YbIMl9kw</t>
@@ -1084,7 +1078,7 @@
     <t>fikCKDWCNp8b</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fikCKDWCNp8b&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sclEwdEVWME5PY0RoaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4tZzdVUkpfeV9sSDVRU1NZelNZS1NxbUh1cjMtRFFLbktzTndVV2FpQnFmWEl6M0RRaGhQM2VBMF80ZGNPcGV2S0U0R2ZISUZQY0JqNmRvRHRGX1JFZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fikCKDWCNp8b&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sclEwdEVWME5PY0RoaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NQ3NRejY2OURiMnpjMDdXeUIySl9lMFNGSXRrQ3RjUkhnZHJ4WXgzd0ZUV2hGeGNUMDlodTFPa0Jkb1FJQzF0ckdlTEdoWUUzaWM5cXJycWRTQ2xSQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx8bhJ8pIlrT</t>
@@ -1096,7 +1090,7 @@
     <t>Screenshot 20250418 at 1.18.53AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiqr4JQRRPfw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seGNqUktVVkpTVUdaM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5YX2VGUUtWTF8zRkpuelNkNzFUQU1TXzM1a2tmV1ZOM3dsLTU0TER5TzNXQWI2X0RWeHVLT1ZNNzl5d21WYkh6Qmt4clZYd2thVW9HUFprbU1pdkMwZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiqr4JQRRPfw&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seGNqUktVVkpTVUdaM0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5fVjMxRnF1b0RfMk1NTXJhM2hZd1ZiMlY5TXNDYXA2OTZLQXQ1MkFwQkdnSS1GTHJPYjlfX25qMkZ3YjR1bTVPT2FEM2F2Tmt1VldwTnluYVl4WGxfQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx7Ml0kpMbnb</t>
@@ -1108,7 +1102,7 @@
     <t>Screenshot 20250418 at 1.03.43AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiqLpU83tjHp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seFRIQlZPRE4wYWtod0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5MN3hLYjQ1ckpvUFRMUWoweFRyb1dFWGVVbEJ6Y2NWZG11MUI2Y2E1YUVNeUdLR0dLTkdjV0NRX0RsVUpoZFVGM193N2d4YlQyTUNRbkx5TnIwSU9MQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiqLpU83tjHp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1seFRIQlZPRE4wYWtod0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5NcXoxMHoxRkdRdzVHOXY5RW84M2RtUXJqbWlqaEItOUp4enktVGRKR2lSSklNZW52YldnYUVSemY2NlJ3VjVtU1JzWEo4VWJHeFZ2Vk5oQ3VTLVlSUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx6BV414xgJq</t>
@@ -1120,7 +1114,7 @@
     <t>Screenshot 20250506 at 6.30.12PM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fifnT3uv4yde&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbWJsUXpkWFkwZVdSbElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5Pc1NwRWI2NWNYcmNHb0h1bGNxSEZQaEhTb3JxLXU1ODFNTjR6ZXpselYxcW92MFBLNGl3eHJtY0wzeW9YZkRuXzFVQzkyUjlybFd5SVRjU2ZkN2s1Zw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fifnT3uv4yde&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbWJsUXpkWFkwZVdSbElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5RUW1XcTNNTHppUTBiNlRNSGJyYlZJaTJic1lkeU9YMzd4U0Y4Y1pSUFFKbFNlclJXZDFUckJEMkN5cm5hX0RSS1ZGa3ctVTJmNFpPeFlWRUtPVnlNZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txzloDonaBUV</t>
@@ -1129,7 +1123,7 @@
     <t>fi4YAINdGYiz</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi4YAINdGYiz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMFdVRkpUbVJIV1dsNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC51UDNxWWJVS1JXdDVJaU91R2FyYWx1UTN4WDNqZHdncWhIeENKUjBGM0JpZHk5VVUwNmdWcm9CSE5vZjFqY2JPdVJ6NGtpR1d2ZnJod2tuRFVGRFJ0QQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi4YAINdGYiz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMFdVRkpUbVJIV1dsNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5zNlQ4Q2xiMVc5aVhrbmhheGF1TnFYc3pFX2pkV3lKLWhSekFBSTlkUldlNEs1cnVLeWVMMlEtSjd1eE9UTUFTdHRnYTNrTG5mREtjemQtMFFUM1diZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txREoi5Jhj0U</t>
@@ -1138,7 +1132,7 @@
     <t>fighLPyRdWkW</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fighLPyRdWkW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbmFFeFFlVkprVjJ0WElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC55aF8yMUttWXFZUXNMT2E1Y3VaSnNLX00wcWk3VWxCMXlPMVZIOHVzcGtUYjZiUFctYjlhQVh5RVprNnVFV2xzbFl0R0JERHJxQjRwaEgxMXdVRG50dw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fighLPyRdWkW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbmFFeFFlVkprVjJ0WElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5xRzFLekJkMVpzX3RSd3l6QzVCX2o4azVZMXQwV094SW9SYlBuMm5MRGJNdkpDTTVzWS1wUVdHQWhNcjFxRExyczFkSU1MM19DQ1FNQWNmTUJPXy1rZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txqv28AQEH1p</t>
@@ -1150,7 +1144,7 @@
     <t>uber_Apr_02_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiIRwQ0cmSAT&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSlVuZFJNR050VTBGVUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5qZnMyT1BJaUNZcElsd01tbFJDR3BZYkl2YjBOd2FqNGk2WjZubXRQMWU1UGZxNXZwY3phV0JpU0w0aVVFR1FoUUdUbkt3Zm9yTUJmaWc3YksyTmZLZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiIRwQ0cmSAT&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSlVuZFJNR050VTBGVUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5peUdRVFV1SUdNQ0RpN2FkdE9LbTVkUXZCZkZneEdHZDJEanpCT1VQbFhRX2NFRmZJODFhcThfSFVaSWFtQ2ZWQVJhX0NmQlBLMkdQMkNqQXNXanBmZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txq3hj9bJh1c</t>
@@ -1162,7 +1156,7 @@
     <t>Screenshot 20250329 at 1.39.51AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNe1C1K75AU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT1pURkRNVXMzTlVGVklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5lSURGeHpsOTAwVzJPY2hMQU9VWUZvd3RLdWRtZVRWVElkQ2wtQ0FhUHZsQkdSanVGV3hZREpRZkdDNG51MjQwa0w0MWplUWhXeDFoUmRDWlFNSHBIdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiNe1C1K75AU&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sT1pURkRNVXMzTlVGVklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC40Qk5PYlYtamVQS2VEbm5hdEk4aEFvc1I3b1QzanYzVXZBS2dad1p4dl8xangyYjZHTzJmTml3bm5Yd1JXdGx1TGFBZVJtQ195bk5fMmJPRE9mOVp0UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txATum7WE1Ri</t>
@@ -1174,7 +1168,7 @@
     <t>Screenshot 20250329 at 1.37.22AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiu0E9LTQcAZ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMU1FVTVURlJSWTBGYUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5MX2VyaDBOaGlhUDgwLWZqR2RvakdUVXhPQk5DNXNONDYtcnQ5eW1iN3BLWmkyblFaNVBxT2ttYWN6Y3VtMVRnbTFVZ1ZrdFNIWGl5VzNBNlV1UG1UUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiu0E9LTQcAZ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMU1FVTVURlJSWTBGYUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56VmUtZkZHaWo0X0otN0xUTUxNV3djc08xTk9Tc3MxaGJKdUdkcUgxMVF1WTJ3UXhOcWFtb2k0S0tpdENtcW96VmZMWWRRSTFtRl9hRVBPRk5GTFU1QQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txzBSZOJd2lU</t>
@@ -1186,7 +1180,7 @@
     <t>uber_Apr_04_2025.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fip05O9Gbrgp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd01EVlBPVWRpY21kd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5HOTNHOWhqUUN4bmJ5TS02dVV0RW9UempCZHNLZk0xVjRleXJUbUY2S0Z3NE9GQ29GRUxkVVF1cG1weE1CbmJ0UmNrc3NhS3gtOGFRVjIwMlp0Wmxxdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fip05O9Gbrgp&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd01EVlBPVWRpY21kd0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56SHkxTF9WWkhzTm1tcS0waGc0OWZ4d1htOWhCWHRkZGd3X2N1aUYwX0xfYnJNbUVlMTRvWHdrZ3M0a2VtWFFtdEwtd0RjQ2k4OE9oT1QzZDhUcDBGZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txTvCHl6ZmsF</t>
@@ -1198,7 +1192,7 @@
     <t>Screenshot 20250329 at 1.56.45AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiH4DTYGnGkx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSU5FUlVXVWR1UjJ0NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5GVFcxZTE0UDlPTW9ybW1nZ3k2dE41Z3UtVXlud0c0Vmt3WGxST096Q1JJTzFHQW1VWmtNS0U2TzlPN1JjYloxWWhiZXNVOXBXdTE2QzlNdUFMX2xHZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiH4DTYGnGkx&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSU5FUlVXVWR1UjJ0NElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5penVONGxFR1VfVUNJaHljWkN2bl9ucVdXa0gydmxVYUNNUDRBRTBUdnR6aUxzSHotZmI2b2VSc3FLeC1TU2JCbWtFWk8tSGtsbTF4ZXM2akh2anRiUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txSr5d4xN0Uf</t>
@@ -1210,13 +1204,13 @@
     <t>taco_0580691032800063_ca54b36fb8f14e70b0c6b2e01447f8a1.pdf</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi98ma7MczG2&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNU9HMWhOMDFqZWtjeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5Rb2VORGJjYnJjUzA1em40RlNVUmVyWkpOcm10R05Wcm5uMDdvOFBReTJUcXp1ZjAxN1dCVGZvcGIzVS1OQ2tjWjQwM254YVRpa1dKZXltWDlPT2VRZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi98ma7MczG2&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rNU9HMWhOMDFqZWtjeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5CZXA0TE9LOTF1NGNRSjE3M2E5Z3BvMWUyX0N3Q3RQLThJOUNhNEpiN0FJRjF5TURGYzJ2eGprNE1YejhuSmJqNW85aDZyT3FnRGV2dk9iZ2pGMzdUdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>fizrtO6WyJPH</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizrtO6WyJPH&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNmNuUlBObGQ1U2xCSUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5Tay1ESTc3TW5jc2VPWGVzak43TGtBMGFmMjhlbFhUSUF6WFpsVnRVUVBWZnhlTWxJa2UtOVpXN0R1Y2JQN2lZYWhaMjRWNUlVTFNqUWpUZDRUV0RBZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fizrtO6WyJPH&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sNmNuUlBObGQ1U2xCSUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5zN1FPVkhRc1poNlVoODlOM3hqV1pmZzZRbGFWUnM4TFljN0RjZmQtcTZLTXVPNXRrQzNOMUVvbm1PYWNCZzFrT2xLMTNkNk1zZ1VfZk4zVEtpNHBxdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txLYIPWychoD</t>
@@ -1225,7 +1219,7 @@
     <t>fiiYqXOfq79f</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiiYqXOfq79f&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scFdYRllUMlp4TnpsbUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5TUUxWUElnckpCbXR4djBPckxkejZMTkNmQXlaZVkwaHhEWTNHT01BWnlkRjVQUnU0SWlvUnNROU9NenRid0NoZjk2ZzA1bmdUQlRtTmxkNVRoODN1dw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiiYqXOfq79f&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scFdYRllUMlp4TnpsbUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5JR1RZcG1sUG4tc2pKZTRxdTgyYldRNG4waElSZ1RYYzJoWmpXZVBocWlodXdxTUdDd1VWZGVPXzRoeEI5TVVLWmNaeUlSOWtVZVNGMjk3WTE2U3g1Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txT3POrlWND6</t>
@@ -1243,7 +1237,7 @@
     <t>ouxAnSzSUyyn</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=filp8sWBEg3r&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sc2NEaHpWMEpGWnpOeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4xX252UkZKb1k4VmdZUV9ZYVVSU1psMTZDeldkYjRZZ1A3eWp4ZUpxeHMyakpfQlRxbEs1Qm5wUzdTd0NhYWMtTDdJUHdZZ1o2WTdWd2J5OHp4U2Q2UQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=filp8sWBEg3r&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sc2NEaHpWMEpGWnpOeUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5wbURKVWlqS1Q4Y2tjY0FzRy1vcmM2dWNvcWtmVURGYkNYNk5rS3FKb01MdC1tQlZuUjJmT2RicktFS0V0eUNUb1p2MER4cVdUbFVGLUtCMC15dkwtUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txXkVsiy4Gj0</t>
@@ -1255,7 +1249,7 @@
     <t>Screenshot 20250120 at 7.25.48PM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiEuAzd8kghD&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRmRVRjZaRGhyWjJoRUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC44MmJtNFJoWTV5bzdvVEhGcl8zRW9vcHNJSHh3ZE5sNGZGSUdkdk15anZmdXpybXRyeUtmYmk5VDBYZktpNHVCS1R3NEZmci1TZF9VX0x2WlFBdTJtdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiEuAzd8kghD&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRmRVRjZaRGhyWjJoRUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5JS2JfbzBfZk54T2NYRzJFOTZFT1NBTnVBbmwyakFOTVhWaGRyTndiUnBlVHBNY09Ud3NrWGFnc0Y3UlMwUFBBdWlQVzYtNHl0WUVhdVlRQ0YxNlY5UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx2PzAtrMSgh</t>
@@ -1264,7 +1258,7 @@
     <t>fitqPeNKvFCc</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitqPeNKvFCc&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMGNWQmxUa3QyUmtOaklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ZaGE3SFZ3d3RMalFuejFyM3pDMldTR2pydWNuRTNYRi1pYlI0UFc0dEJQRGFIaElPU2lSUzRhT1dLNXBpTkM0bEMwS09ZZFRiNUtvS2N2QUJTbXc4Zw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fitqPeNKvFCc&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sMGNWQmxUa3QyUmtOaklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5GTWpWcXlsZWxYUGEwdzNzMlM4bFBLTVBlV1o4aVh5dTBtZmdHVUl3bTQ5X2h2TGV3YWkxYXc0cWNxdERfR05mcmlLc0l2X3lmcE56b0xLT1pvRzdjUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txrjE3UEj70o</t>
@@ -1273,7 +1267,7 @@
     <t>fiKTta8Frcj2</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiKTta8Frcj2&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTFZIUmhPRVp5WTJveUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5iS2V3VDRBYUNtM0xNOU9rOVVicGNMbzZiMnAyYmlzU0JWb2otMDVWSkVmX3N4SlkxNjlOeThtSzhlOEhjT3YtTDV0UDV2OWlnd2ZkOUtHNlo1eVJUdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiKTta8Frcj2&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTFZIUmhPRVp5WTJveUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5QRWJyYlRyZ3otMFpyYzJIWEJXRjM1RHAwbnB0OHI0ZFo4NFpQakh4enhEeFd3TFA3NTFYN2dWV0gtNHhrZ1ZYNWtKcTBGc19mTnZ0WnM4Q0JjVk0yUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txz0JKFL2q32</t>
@@ -1282,7 +1276,7 @@
     <t>fiZZzcgUxLz5</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZZzcgUxLz5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYVducGpaMVY0VEhvMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5SaWh5ZVdZNTJUeWVpamUya0d4UWNkVEVoaVd4OE5yaTBiNGNjVy1WUXV3dThRaWlOVlVQNXlJYVRmMzlHaFRSbjY1LVZ4T2VRZTN2YWtzdENXUlVDQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiZZzcgUxLz5&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sYVducGpaMVY0VEhvMUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5wcjMtMlVRbEdNMnhMY2FUUy1aYlhyNkwxaERtOUpFTEMwXzRmejE4ZkoxUW5qNnhmWUhCQ1o2ZFlsT3d1ZlhTZDJzZG8zLVdjbVRvZ2NZNTVLRFVfQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txTtbRefb7Bx</t>
@@ -1291,7 +1285,7 @@
     <t>fiIgHrw09RAW</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiIgHrw09RAW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSlowaHlkekE1VWtGWElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ZZFhtV3kwbmtmSXRwOFh4a3E5VXZSM1RwTVU4N1dSV2g1QVVZdWQ4RXJ6U2MzbEd1X0NnUlFTWXVMTlVaekxMb0VjcTlRRGl0Q0FlYWR6cFdSRmJDZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiIgHrw09RAW&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sSlowaHlkekE1VWtGWElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4wcnBHZkhaTHdYNVVpd2oyXzVZdmFubUhhdndSUmtYZzNXV1NPd0RUZmI3REZLS1NZb3Noc0c1N01ubXdFUTF1b1ljMEJiUWhIS09vNi05a0tlYm5EQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txmWXGD8ZGVl</t>
@@ -1300,7 +1294,7 @@
     <t>fi6XJe46E6t8</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6XJe46E6t8&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMldFcGxORFpGTm5RNElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ZNjR3TExFbmRvU1E5c1hFZU9sd2FIN2VPLVNyUXVpMnhIOEdXSHdVTTNZRXZPeXk2NEZtVmplX1dPYy1nVEVIc19Zb1dkQk5YTjBKWVE3UWVVczdCZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fi6XJe46E6t8&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1rMldFcGxORFpGTm5RNElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56VDFObkJ0TW9GQUJkSDk1dzlfdDlFa1VEc3NkMGhrZGlXM1N5RmpDS0xkT0hfWkVESDNvZGMyc0dkUXVrNmkycDdQN2tPOFNKZjViMV8tV21RdlVHQQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txlh21azFyKa</t>
@@ -1312,7 +1306,7 @@
     <t>Screenshot 20250124 at 9.21.31PM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fib37CjWlJIz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saU16ZERhbGRzU2tsNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5VWlJRQ3JENjBaRW1fZnBQTV92M01tOXdtZ3g1eWpQVE53eFQ0WldlcGtOZjI0c2lNejBGX053aXZhUDVELUdEYjB0R1VzbkE3aEhra3B5TllQOWNXZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fib37CjWlJIz&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saU16ZERhbGRzU2tsNklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC51S1ZLaE82cUlqLWtBNzgzTGVOR2xVVUpMeVVGVGR5NUhGdEZBREhqc3ZNeXBiVWMzemo0Y0ZKWXNNS0tpY3EtTGFnWlU5OWZmQ1Rfa3ZIcGpFdzZuUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txHUwgeynkYX</t>
@@ -1321,7 +1315,7 @@
     <t>fiLVieqZMgKH</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiLVieqZMgKH&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTVZtbGxjVnBOWjB0SUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5qRWhfRl9fTlRNNEJyUFVEb25mbUdmV1ZmaXRILXZCNjlHbmhra2dmTDFFTHJWN1FObFNlY3k5N2lpNURMc0N4THd3YU5hc3VIRnB2eVUybHFEYlN5Zw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiLVieqZMgKH&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTVZtbGxjVnBOWjB0SUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5fbWtjbXN2TWFQZ0M1X08zMVMxT3E5YWt6bW9aVU1kU2c3S0ozSWNfMEs3Tmh6LU5rY05LOGUweDVwN2c1Qkl1UEJPV01JRTNtM21qbkoyOURKanFpUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txtFe8YQMuEd</t>
@@ -1330,7 +1324,7 @@
     <t>fiSyQM8EoYjO</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSyQM8EoYjO&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGVWRk5PRVZ2V1dwUElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5zV2VoVEpDYzdnNnFOSWwtekEwb0d3bzZVT2FKRjUzXzA3WHA2UjdnbjFqaElpZ3J6c1UwbmdJeVlyOXdkNGVvMlZha3gweUtFTVppTDZVUXhIRzk2UQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSyQM8EoYjO&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGVWRk5PRVZ2V1dwUElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5oeFpTOVlkLWZwaEJ6MUh4SGFWV1dZSnBmcmhSMnp3RUlSOF9vWmw3RHVPUFhlQWg5WDktdmlJZzZ4RDVmeFRnMWRfNmgwY2hLa3FLbnVpaWh0cHM1Zw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txjnG2E9VbXz</t>
@@ -1342,7 +1336,7 @@
     <t>Screenshot 20250124 at 9.21.41PM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiEdqshvsNu4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRlpIRnphSFp6VG5VMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC4yLS1NNHZ1V1dtMFRzby1NNFdOWEtISjd5Z19UWl9LdlNhdTlHZlFJUEJRQUY5cjd5RG9CZzhMOTN6dzljb3RqTk1FMjF3akJ5QUtIdUlIdzlIaEpuQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiEdqshvsNu4&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sRlpIRnphSFp6VG5VMElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5DdW5ManFlSEc5SjFpZ1FDUE11ZVJ1QWt5M0xaUDc1OFZWbzNyc1FyUmlubHgzSEZ1ZTF6eTZuN2hyVk0wRTFfRlJyb3RRS1hyS1FLSFIyblNIVjB1QQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txdGmU5aEkGe</t>
@@ -1351,7 +1345,7 @@
     <t>fiKFIFWFxrO6</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiKFIFWFxrO6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTFJrbEdWMFo0Y2s4Mklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5BVVA0bnE1dXhFRjZSTE9uNnJYSWhscVQ5OUFaLU1sZ013Q3lzSVZ6blpzdHpVbzN6dkJWYXc5SUVyYTN3N09nNUlqTE9HOThfcG1BTHY1TWRFVWxzUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiKFIFWFxrO6&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sTFJrbEdWMFo0Y2s4Mklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC43YldjcXozYW9adWphX1Y3NzVwanZjSnZXNVFWMTAtdHNuMjFZSl9ucjduNEozempEMERHaVRoVXY4TTdBWXNuOElHQ014UjFGYjRPMHFQSUtlem5GUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txyGt4TLYAXu</t>
@@ -1360,7 +1354,7 @@
     <t>fiPauysVeQkJ</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPauysVeQkJ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUVlYVjVjMVpsVVd0S0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5RYmFmLWNvNFhaaHc5LTRDZVNYR3pyemp5YzR2elc3cUZqNEZoNklxa2lfNTZWZDhKUXdwaXd0ejJ3NnVpR1p4NGtjVkRHdV9sSkMzV2ZQVlB6MC1OQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiPauysVeQkJ&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sUVlYVjVjMVpsVVd0S0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5JVDNYcnFRT2J0MU9qRE1RQnlDTThsSkhWQlJZbFNYeXBwSTJIVy1QNmgzSXo5OXJKVENUTktnYnFLNmhac1VJdDB6RmtPWVBDTTU1VUJmNGctUjladw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txtql8coCmVS</t>
@@ -1372,7 +1366,7 @@
     <t>Screenshot 20250320 at 12.59.25AM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipXrh7dlkvv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1dISm9OMlJzYTNaMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5jd3g1WW4xZktyTFRScDJESUF5M0pidFk2MC1NZGJjWUdOV3Y5ZEVFRkFZNklMYldicFIycUxibFBUWkVNSlkzakRYMk83eGFWTWJ6Tk1NZ0tBTTJCQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fipXrh7dlkvv&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sd1dISm9OMlJzYTNaMklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5KR1JaN2lmYVBDMHZrWUJLTE1NUWlReG5qMVI0Ymp2R0NGdnoxSVhyTXc1ZURHVkRSeDFYQzdEODlvR0x0ZUU5ZXE2S2VwNE1jQkZtaUh5OEdOcXNNdw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txRdQKYx2qCl</t>
@@ -1381,7 +1375,7 @@
     <t>fibREU6ienVb</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fibREU6ienVb&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saVVrVlZObWxsYmxaaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5sekRNNFhyOTBRTUc5YVdXZVpRVzRzS0FiSzRmVFZNYk5hVDZyTjZQNXpEeEhaVjU4UHpraC1udjZJSU5ISlZ1VGVmblptSjJSWTM1d2lWVUdUbGFSQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fibREU6ienVb&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saVVrVlZObWxsYmxaaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5ZMUNPUGVTaDJTLWpKSmJjREMxQUNhTU1lMkRyZGEyM0Qtdno4QkRwQTFub3BMQW1vdjk3b3c4dVgyOUNvUlZnZU5GVFliREpEN05zc29HcjFTZjNBUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txfBhvQ6J2Sy</t>
@@ -1393,7 +1387,7 @@
     <t>Screenshot 20250129 at 9.19.00PM.png</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWUuFx1G1OB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFZYVkdlREZITVU5Q0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC40YWktTm9xVXp1OW1sVmZFeFBfVUZ5VUFuWXRiZktOSjhCSzExYmtvdTNqMHRYZXhueUhBN1QzWGtKRmRqSHFxdUFsYWRTY1AzVF9yRUx1YlU4cWRjZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiWUuFx1G1OB&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sWFZYVkdlREZITVU5Q0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5wd3EwT2RjTlRUdmc3TF8zRnJ5Qk1DMmI1X24xZF9PZGFPOFJfd0ZpUEtEM3BJU3JrMkY4bzBtUjZfVXNUTmk1RDh5X054Q25jR1ZDMHd4Q1FsNDlkZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx4e9SvrjH4r</t>
@@ -1402,7 +1396,7 @@
     <t>fieIFdWd24Dg</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieIFdWd24Dg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFNVWmtWMlF5TkVSbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5Ga3hPTG1PR3JJN2NCVElzNlpLbk9jenp1X29KeE5qYV9qRzNrOVBxNUdVUElkMUFjbkZzOTFya3Mta0F0YW1qdkdRZzQ1Z0RkZkptSlJldGtkVWZJQQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fieIFdWd24Dg&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbFNVWmtWMlF5TkVSbklpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC54SEhKS2lCLUJhQ2c1X1JfQzhrcC1aZ1NOOG1KZDdiV2h6S2tkOG91WkVsRUJoRkhLckJSZ2tzbVh3bnJmMWdjQXlWRDNLZ0RQVU9VNEZwWWZ5MjM0QQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txsoFRus9WIi</t>
@@ -1411,7 +1405,7 @@
     <t>fifXG82n9CB9</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fifXG82n9CB9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbVdFYzRNbTQ1UTBJNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5ZZjEtSkM0QXg4U1RZWGdaZHNIeW5YVm5JZlpNZWV2U1QtSWx0NnR4SkNaX2lTaDRkOWFuY05HU3FFVmtmWVk4SGpIVjVzMWFwSzcxdHhRWFVPZC1lUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fifXG82n9CB9&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbVdFYzRNbTQ1UTBJNUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5Oa1VRcmtuVTZJSEFmQ1NtcmdNNzNuemxSTjk3bkkzcGFYdV9LN0hSMjhwbVY5eTc3VDlENEJnVWZPSEY5NHVZcTNUMHVpNnZyR2d6R2NZRmRLVHc3UQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txSXEPp1i6Qs</t>
@@ -1420,7 +1414,7 @@
     <t>ficYZAQsIZXh</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=ficYZAQsIZXh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saldWcEJVWE5KV2xob0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5MbG5iZWtuN0NTX0gxelZOcUpFY0tIcngyazBpMGdXcFZpaXZKVHAxS09ick9pdVhycHlnaWhYZFN5M1h2cUVIX0E2SmdmQ2dPNVVfb3FBVGdfb2hPUQ%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=ficYZAQsIZXh&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1saldWcEJVWE5KV2xob0lpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC5aNFlFN1RjNDJtek01bzF6dDhOWWR6QTU5dVU5YTEtd2pRTXY5SV8wZXFZN01VV2lGZGxtMmlFNEZOX2FmU21Cc2RpSVZoRGNJMi1GUVE2SHJZd19BUQ%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txt4nFlkRTpe</t>
@@ -1429,7 +1423,7 @@
     <t>fiSsTHRT3gTC</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSsTHRT3gTC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGMxUklVbFF6WjFSRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5iVnRQcEdjbG1LekFSdVk4NC1ZV2QteWhfcEpGQVlJWjViSF9Ib1hPSFZOOU1YMllwdlFNZXJTQjdvT3NYcGZEU0N5bXIwV1pXTnFSc0FJVHJIallqdw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiSsTHRT3gTC&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sVGMxUklVbFF6WjFSRElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC4zUnVVcVc4MWc1dHBYd0o5ajNUNUZrdV9YU2d1SjBnRlByeHF1dlUya2pkMW5hb0NUU0g1RHdYMWVWYjFRRHZNU1lvU0tQTXltTXFoVGhuTGNBREhFZw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>txfpwXvAFLxC</t>
@@ -1438,7 +1432,7 @@
     <t>figuWVn8xHNK</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=figuWVn8xHNK&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbmRWZFdiamg0U0U1TElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC43a2VqOE14RXVRTUIxTVBIV21BOUlGaThJRl8tVUhoYzRSU0t1V1lUbzZ5ZDlxMXhkUDVNbDQ1VzFkb3I1WDRLQlpqLW1Td3Vfa05MRUFBa3YydjNoZw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=figuWVn8xHNK&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1sbmRWZFdiamg0U0U1TElpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC56c1Nva2NGeU9NeFZhOXVncS0wU1FUSTZtNU9TdkVabXFya0pXREdHd0VoWS10M3NPajJ0cE5oa3k5SEhzRTAwd2RRWTBxWERNbDh5SVhfRzlzdWdldw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
   <si>
     <t>tx8n9s6hRjjz</t>
@@ -1447,7 +1441,7 @@
     <t>fiiEIBVbICxb</t>
   </si>
   <si>
-    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiiEIBVbICxb&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scFJVbENWbUpKUTNoaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek14TkRjM056TXNJbWxoZENJNk1UYzNNVGcxTVRjM00zMC5EZWlDbWVzZE83MnZBOUc1eXRSdTZIWkc5amg3bk5hUDQtQXJhNFRWdnRIdU0yQ2R0LTlRcmdJTEtaSlluRllnYWVmVkl4LUhOaWVjZzEzaG40Z3k0Zw%3D%3D&amp;X-Fyle-Issued-At=1771851773&amp;X-Fyle-Expires-At=1773147773</t>
+    <t>https://in1.fylehq.com/platform/v1/admin/files/download?id=fiiEIBVbICxb&amp;X-Fyle-Signature=v2.ZXlKaGJHY2lPaUpGVXpJMU5pSXNJblI1Y0NJNklrcFhWQ0o5LmV5SnRaWFJvYjJRaU9pSkhSVlFpTENKd1lYUm9Jam9pTDNCc1lYUm1iM0p0TDNZeEwyRmtiV2x1TDJacGJHVnpMMlJ2ZDI1c2IyRmtJaXdpY1hWbGNubGZjR0Z5WVcxeklqb2lhV1E5Wm1scFJVbENWbUpKUTNoaUlpd2liM0puWDNWelpYSmZhV1FpT2lKdmRUTmlkVkYwV21GMFlqRWlMQ0owY0dGZmFXUWlPaUowY0dGblNWTldTM2h1VVUxeUlpd2liM0puWDJsa0lqb2liM0k0VkhWU01WWk1kMVZxSWl3aWRYTmxjbDlwWkNJNkluVnplRWRuVEcxc2FFZEpiaUlzSW5KdmJHVnpJam9pUVVSTlNVNHNUMWRPUlZJc1JsbE1SVklzUVVORFQxVk9WRUZPVkNJc0luTmpiM0JsY3lJNklpSXNJbUZzYkc5M1pXUmZRMGxFVW5NaU9pSWlMQ0psZUhBaU9qRTNOek0wTnprME1UUXNJbWxoZENJNk1UYzNNakU0TXpReE5IMC50NlQ1Nm0tWU5kM0lvMUpSa21zMmt1NGJaTEZZZFFKb2xaX3FNTHRES1lTSkgwOVVoVWlpRVR5X3NqN3J1T0IwRUQ4b2JaRWpuM3RWMFQ0UDNrSERidw%3D%3D&amp;X-Fyle-Issued-At=1772183414&amp;X-Fyle-Expires-At=1773479414</t>
   </si>
 </sst>
 </file>
@@ -1978,7 +1972,7 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
@@ -1987,13 +1981,13 @@
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
         <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>34</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -2007,25 +2001,25 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>38</v>
@@ -2042,28 +2036,28 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
@@ -2077,28 +2071,28 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
         <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" t="s">
-        <v>46</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -2112,28 +2106,28 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
         <v>47</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>48</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" t="s">
-        <v>51</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
@@ -2147,28 +2141,28 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
         <v>52</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
         <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" t="s">
-        <v>54</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
@@ -2182,28 +2176,28 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
         <v>55</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
         <v>56</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
-      </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
@@ -2217,13 +2211,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
@@ -2232,10 +2226,10 @@
         <v>15</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>61</v>
@@ -2258,7 +2252,7 @@
         <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -2267,10 +2261,10 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>64</v>
@@ -2302,10 +2296,10 @@
         <v>15</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G14" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>68</v>
@@ -2337,10 +2331,10 @@
         <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H15" t="s">
         <v>71</v>
@@ -2372,10 +2366,10 @@
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H16" t="s">
         <v>75</v>
@@ -2407,10 +2401,10 @@
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H17" t="s">
         <v>78</v>
@@ -2442,10 +2436,10 @@
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G18" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H18" t="s">
         <v>81</v>
@@ -2477,10 +2471,10 @@
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
         <v>85</v>
@@ -2512,10 +2506,10 @@
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
         <v>89</v>
@@ -2547,10 +2541,10 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
         <v>93</v>
@@ -2582,10 +2576,10 @@
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
         <v>97</v>
@@ -2617,10 +2611,10 @@
         <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H23" t="s">
         <v>101</v>
@@ -2652,10 +2646,10 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G24" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H24" t="s">
         <v>105</v>
@@ -2687,10 +2681,10 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G25" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H25" t="s">
         <v>109</v>
@@ -2722,10 +2716,10 @@
         <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H26" t="s">
         <v>112</v>
@@ -2757,10 +2751,10 @@
         <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H27" t="s">
         <v>115</v>
@@ -2792,10 +2786,10 @@
         <v>15</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
         <v>119</v>
@@ -2827,10 +2821,10 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
         <v>122</v>
@@ -2862,10 +2856,10 @@
         <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
         <v>125</v>
@@ -2897,10 +2891,10 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
         <v>128</v>
@@ -2932,10 +2926,10 @@
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H32" t="s">
         <v>132</v>
@@ -2967,10 +2961,10 @@
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H33" t="s">
         <v>135</v>
@@ -3002,10 +2996,10 @@
         <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s">
         <v>138</v>
@@ -3037,10 +3031,10 @@
         <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s">
         <v>141</v>
@@ -3072,10 +3066,10 @@
         <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s">
         <v>144</v>
@@ -3107,10 +3101,10 @@
         <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H37" t="s">
         <v>147</v>
@@ -3142,10 +3136,10 @@
         <v>15</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H38" t="s">
         <v>150</v>
@@ -3177,10 +3171,10 @@
         <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H39" t="s">
         <v>154</v>
@@ -3212,10 +3206,10 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
         <v>158</v>
@@ -3247,10 +3241,10 @@
         <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H41" t="s">
         <v>161</v>
@@ -3282,10 +3276,10 @@
         <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H42" t="s">
         <v>164</v>
@@ -3317,10 +3311,10 @@
         <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H43" t="s">
         <v>167</v>
@@ -3352,10 +3346,10 @@
         <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H44" t="s">
         <v>170</v>
@@ -3387,10 +3381,10 @@
         <v>15</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H45" t="s">
         <v>173</v>
@@ -3422,10 +3416,10 @@
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s">
         <v>176</v>
@@ -3457,10 +3451,10 @@
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H47" t="s">
         <v>179</v>
@@ -3492,10 +3486,10 @@
         <v>15</v>
       </c>
       <c r="F48" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H48" t="s">
         <v>183</v>
@@ -3527,10 +3521,10 @@
         <v>15</v>
       </c>
       <c r="F49" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H49" t="s">
         <v>186</v>
@@ -3562,10 +3556,10 @@
         <v>15</v>
       </c>
       <c r="F50" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H50" t="s">
         <v>190</v>
@@ -3597,10 +3591,10 @@
         <v>15</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H51" t="s">
         <v>194</v>
@@ -3632,10 +3626,10 @@
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s">
         <v>198</v>
@@ -3667,10 +3661,10 @@
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H53" t="s">
         <v>201</v>
@@ -3702,10 +3696,10 @@
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H54" t="s">
         <v>204</v>
@@ -3737,10 +3731,10 @@
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H55" t="s">
         <v>207</v>
@@ -3772,10 +3766,10 @@
         <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
         <v>210</v>
@@ -3807,10 +3801,10 @@
         <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s">
         <v>214</v>
@@ -3842,10 +3836,10 @@
         <v>15</v>
       </c>
       <c r="F58" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s">
         <v>217</v>
@@ -3877,10 +3871,10 @@
         <v>15</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
         <v>220</v>
@@ -3912,10 +3906,10 @@
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G60" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s">
         <v>224</v>
@@ -3938,19 +3932,19 @@
         <v>226</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D61" t="s">
         <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F61" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G61" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s">
         <v>227</v>
@@ -3979,13 +3973,13 @@
         <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F62" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G62" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>230</v>
@@ -4017,10 +4011,10 @@
         <v>15</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s">
         <v>234</v>
@@ -4052,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
         <v>238</v>
@@ -4087,10 +4081,10 @@
         <v>15</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H65" t="s">
         <v>242</v>
@@ -4122,10 +4116,10 @@
         <v>15</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G66" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H66" t="s">
         <v>246</v>
@@ -4157,19 +4151,19 @@
         <v>15</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G67" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H67" t="s">
         <v>250</v>
       </c>
       <c r="I67" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K67" t="s">
         <v>21</v>
@@ -4177,34 +4171,34 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>251</v>
+      </c>
+      <c r="B68" t="s">
+        <v>252</v>
+      </c>
+      <c r="C68" t="s">
         <v>253</v>
       </c>
-      <c r="B68" t="s">
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" t="s">
+        <v>56</v>
+      </c>
+      <c r="G68" t="s">
+        <v>57</v>
+      </c>
+      <c r="H68" t="s">
         <v>254</v>
       </c>
-      <c r="C68" t="s">
-        <v>255</v>
-      </c>
-      <c r="D68" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" t="s">
-        <v>17</v>
-      </c>
-      <c r="H68" t="s">
-        <v>256</v>
-      </c>
       <c r="I68" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s">
         <v>21</v>
@@ -4212,34 +4206,34 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>255</v>
+      </c>
+      <c r="B69" t="s">
+        <v>256</v>
+      </c>
+      <c r="C69" t="s">
         <v>257</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G69" t="s">
+        <v>57</v>
+      </c>
+      <c r="H69" t="s">
         <v>258</v>
       </c>
-      <c r="C69" t="s">
-        <v>259</v>
-      </c>
-      <c r="D69" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F69" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" t="s">
-        <v>17</v>
-      </c>
-      <c r="H69" t="s">
-        <v>260</v>
-      </c>
       <c r="I69" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K69" t="s">
         <v>21</v>
@@ -4247,34 +4241,34 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>259</v>
+      </c>
+      <c r="B70" t="s">
+        <v>260</v>
+      </c>
+      <c r="C70" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" t="s">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s">
+        <v>37</v>
+      </c>
+      <c r="F70" t="s">
+        <v>56</v>
+      </c>
+      <c r="G70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H70" t="s">
         <v>261</v>
       </c>
-      <c r="B70" t="s">
-        <v>262</v>
-      </c>
-      <c r="C70" t="s">
-        <v>49</v>
-      </c>
-      <c r="D70" t="s">
-        <v>14</v>
-      </c>
-      <c r="E70" t="s">
-        <v>50</v>
-      </c>
-      <c r="F70" t="s">
-        <v>16</v>
-      </c>
-      <c r="G70" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" t="s">
-        <v>263</v>
-      </c>
       <c r="I70" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K70" t="s">
         <v>21</v>
@@ -4282,34 +4276,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B71" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>37</v>
+      </c>
+      <c r="F71" t="s">
+        <v>56</v>
+      </c>
+      <c r="G71" t="s">
+        <v>57</v>
+      </c>
+      <c r="H71" t="s">
         <v>264</v>
       </c>
-      <c r="C71" t="s">
-        <v>265</v>
-      </c>
-      <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s">
-        <v>50</v>
-      </c>
-      <c r="F71" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" t="s">
-        <v>17</v>
-      </c>
-      <c r="H71" t="s">
-        <v>266</v>
-      </c>
       <c r="I71" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J71" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K71" t="s">
         <v>21</v>
@@ -4317,34 +4311,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>265</v>
+      </c>
+      <c r="B72" t="s">
+        <v>266</v>
+      </c>
+      <c r="C72" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" t="s">
+        <v>56</v>
+      </c>
+      <c r="G72" t="s">
+        <v>57</v>
+      </c>
+      <c r="H72" t="s">
         <v>267</v>
       </c>
-      <c r="B72" t="s">
-        <v>268</v>
-      </c>
-      <c r="C72" t="s">
-        <v>49</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s">
-        <v>50</v>
-      </c>
-      <c r="F72" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" t="s">
-        <v>17</v>
-      </c>
-      <c r="H72" t="s">
-        <v>269</v>
-      </c>
       <c r="I72" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J72" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K72" t="s">
         <v>21</v>
@@ -4352,34 +4346,34 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B73" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C73" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H73" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I73" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J73" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K73" t="s">
         <v>21</v>
@@ -4387,34 +4381,34 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" t="s">
+        <v>271</v>
+      </c>
+      <c r="C74" t="s">
+        <v>263</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s">
+        <v>37</v>
+      </c>
+      <c r="F74" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74" t="s">
+        <v>57</v>
+      </c>
+      <c r="H74" t="s">
         <v>272</v>
       </c>
-      <c r="B74" t="s">
-        <v>273</v>
-      </c>
-      <c r="C74" t="s">
-        <v>265</v>
-      </c>
-      <c r="D74" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" t="s">
-        <v>50</v>
-      </c>
-      <c r="F74" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" t="s">
-        <v>17</v>
-      </c>
-      <c r="H74" t="s">
-        <v>274</v>
-      </c>
       <c r="I74" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J74" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K74" t="s">
         <v>21</v>
@@ -4422,34 +4416,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C75" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G75" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H75" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I75" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K75" t="s">
         <v>21</v>
@@ -4457,34 +4451,34 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>275</v>
+      </c>
+      <c r="B76" t="s">
+        <v>276</v>
+      </c>
+      <c r="C76" t="s">
         <v>277</v>
       </c>
-      <c r="B76" t="s">
+      <c r="D76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76" t="s">
+        <v>57</v>
+      </c>
+      <c r="H76" t="s">
         <v>278</v>
       </c>
-      <c r="C76" t="s">
-        <v>279</v>
-      </c>
-      <c r="D76" t="s">
-        <v>14</v>
-      </c>
-      <c r="E76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" t="s">
-        <v>16</v>
-      </c>
-      <c r="G76" t="s">
-        <v>17</v>
-      </c>
-      <c r="H76" t="s">
-        <v>280</v>
-      </c>
       <c r="I76" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K76" t="s">
         <v>21</v>
@@ -4492,34 +4486,34 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>279</v>
+      </c>
+      <c r="B77" t="s">
+        <v>280</v>
+      </c>
+      <c r="C77" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>37</v>
+      </c>
+      <c r="F77" t="s">
+        <v>56</v>
+      </c>
+      <c r="G77" t="s">
+        <v>57</v>
+      </c>
+      <c r="H77" t="s">
         <v>281</v>
       </c>
-      <c r="B77" t="s">
-        <v>282</v>
-      </c>
-      <c r="C77" t="s">
-        <v>49</v>
-      </c>
-      <c r="D77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" t="s">
-        <v>50</v>
-      </c>
-      <c r="F77" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" t="s">
-        <v>283</v>
-      </c>
       <c r="I77" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K77" t="s">
         <v>21</v>
@@ -4527,34 +4521,34 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B78" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C78" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="H78" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I78" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K78" t="s">
         <v>21</v>
@@ -4562,34 +4556,34 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>284</v>
+      </c>
+      <c r="B79" t="s">
+        <v>285</v>
+      </c>
+      <c r="C79" t="s">
         <v>286</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" t="s">
         <v>287</v>
       </c>
-      <c r="C79" t="s">
-        <v>288</v>
-      </c>
-      <c r="D79" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" t="s">
-        <v>32</v>
-      </c>
-      <c r="G79" t="s">
-        <v>33</v>
-      </c>
-      <c r="H79" t="s">
-        <v>289</v>
-      </c>
       <c r="I79" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K79" t="s">
         <v>21</v>
@@ -4597,34 +4591,34 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>288</v>
+      </c>
+      <c r="B80" t="s">
+        <v>289</v>
+      </c>
+      <c r="C80" t="s">
         <v>290</v>
       </c>
-      <c r="B80" t="s">
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" t="s">
         <v>291</v>
       </c>
-      <c r="C80" t="s">
-        <v>292</v>
-      </c>
-      <c r="D80" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" t="s">
-        <v>32</v>
-      </c>
-      <c r="G80" t="s">
-        <v>33</v>
-      </c>
-      <c r="H80" t="s">
-        <v>293</v>
-      </c>
       <c r="I80" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K80" t="s">
         <v>21</v>
@@ -4632,34 +4626,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>292</v>
+      </c>
+      <c r="B81" t="s">
+        <v>293</v>
+      </c>
+      <c r="C81" t="s">
         <v>294</v>
       </c>
-      <c r="B81" t="s">
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>37</v>
+      </c>
+      <c r="F81" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" t="s">
         <v>295</v>
       </c>
-      <c r="C81" t="s">
-        <v>296</v>
-      </c>
-      <c r="D81" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" t="s">
-        <v>50</v>
-      </c>
-      <c r="F81" t="s">
-        <v>32</v>
-      </c>
-      <c r="G81" t="s">
-        <v>33</v>
-      </c>
-      <c r="H81" t="s">
-        <v>297</v>
-      </c>
       <c r="I81" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K81" t="s">
         <v>21</v>
@@ -4667,34 +4661,34 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B82" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C82" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
         <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I82" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K82" t="s">
         <v>21</v>
@@ -4702,10 +4696,10 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B83" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C83" t="s">
         <v>233</v>
@@ -4717,19 +4711,19 @@
         <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I83" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K83" t="s">
         <v>21</v>
@@ -4737,10 +4731,10 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B84" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C84" t="s">
         <v>233</v>
@@ -4752,19 +4746,19 @@
         <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I84" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K84" t="s">
         <v>21</v>
@@ -4772,10 +4766,10 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B85" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C85" t="s">
         <v>233</v>
@@ -4787,19 +4781,19 @@
         <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I85" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J85" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K85" t="s">
         <v>21</v>
@@ -4807,34 +4801,34 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>307</v>
+      </c>
+      <c r="B86" t="s">
+        <v>308</v>
+      </c>
+      <c r="C86" t="s">
         <v>309</v>
       </c>
-      <c r="B86" t="s">
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" t="s">
         <v>310</v>
       </c>
-      <c r="C86" t="s">
+      <c r="F86" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" t="s">
         <v>311</v>
       </c>
-      <c r="D86" t="s">
-        <v>14</v>
-      </c>
-      <c r="E86" t="s">
-        <v>312</v>
-      </c>
-      <c r="F86" t="s">
-        <v>32</v>
-      </c>
-      <c r="G86" t="s">
-        <v>33</v>
-      </c>
-      <c r="H86" t="s">
-        <v>313</v>
-      </c>
       <c r="I86" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K86" t="s">
         <v>21</v>
@@ -4842,34 +4836,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>312</v>
+      </c>
+      <c r="B87" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" t="s">
         <v>314</v>
       </c>
-      <c r="B87" t="s">
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" t="s">
         <v>315</v>
       </c>
-      <c r="C87" t="s">
-        <v>316</v>
-      </c>
-      <c r="D87" t="s">
-        <v>14</v>
-      </c>
-      <c r="E87" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" t="s">
-        <v>32</v>
-      </c>
-      <c r="G87" t="s">
-        <v>33</v>
-      </c>
-      <c r="H87" t="s">
-        <v>317</v>
-      </c>
       <c r="I87" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J87" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K87" t="s">
         <v>21</v>
@@ -4877,34 +4871,34 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>316</v>
+      </c>
+      <c r="B88" t="s">
+        <v>317</v>
+      </c>
+      <c r="C88" t="s">
         <v>318</v>
       </c>
-      <c r="B88" t="s">
+      <c r="D88" t="s">
+        <v>14</v>
+      </c>
+      <c r="E88" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" t="s">
         <v>319</v>
       </c>
-      <c r="C88" t="s">
-        <v>320</v>
-      </c>
-      <c r="D88" t="s">
-        <v>14</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>32</v>
-      </c>
-      <c r="G88" t="s">
-        <v>33</v>
-      </c>
-      <c r="H88" t="s">
-        <v>321</v>
-      </c>
       <c r="I88" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K88" t="s">
         <v>21</v>
@@ -4912,34 +4906,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>320</v>
+      </c>
+      <c r="B89" t="s">
+        <v>321</v>
+      </c>
+      <c r="C89" t="s">
         <v>322</v>
       </c>
-      <c r="B89" t="s">
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" t="s">
         <v>323</v>
       </c>
-      <c r="C89" t="s">
-        <v>324</v>
-      </c>
-      <c r="D89" t="s">
-        <v>14</v>
-      </c>
-      <c r="E89" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" t="s">
-        <v>32</v>
-      </c>
-      <c r="G89" t="s">
-        <v>33</v>
-      </c>
-      <c r="H89" t="s">
-        <v>325</v>
-      </c>
       <c r="I89" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K89" t="s">
         <v>21</v>
@@ -4947,34 +4941,34 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>324</v>
+      </c>
+      <c r="B90" t="s">
+        <v>325</v>
+      </c>
+      <c r="C90" t="s">
+        <v>309</v>
+      </c>
+      <c r="D90" t="s">
+        <v>14</v>
+      </c>
+      <c r="E90" t="s">
+        <v>310</v>
+      </c>
+      <c r="F90" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" t="s">
         <v>326</v>
       </c>
-      <c r="B90" t="s">
-        <v>327</v>
-      </c>
-      <c r="C90" t="s">
-        <v>311</v>
-      </c>
-      <c r="D90" t="s">
-        <v>14</v>
-      </c>
-      <c r="E90" t="s">
-        <v>312</v>
-      </c>
-      <c r="F90" t="s">
-        <v>32</v>
-      </c>
-      <c r="G90" t="s">
-        <v>33</v>
-      </c>
-      <c r="H90" t="s">
-        <v>328</v>
-      </c>
       <c r="I90" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J90" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K90" t="s">
         <v>21</v>
@@ -4982,34 +4976,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>327</v>
+      </c>
+      <c r="B91" t="s">
+        <v>328</v>
+      </c>
+      <c r="C91" t="s">
         <v>329</v>
       </c>
-      <c r="B91" t="s">
+      <c r="D91" t="s">
+        <v>14</v>
+      </c>
+      <c r="E91" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" t="s">
         <v>330</v>
       </c>
-      <c r="C91" t="s">
-        <v>331</v>
-      </c>
-      <c r="D91" t="s">
-        <v>14</v>
-      </c>
-      <c r="E91" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" t="s">
-        <v>32</v>
-      </c>
-      <c r="G91" t="s">
-        <v>33</v>
-      </c>
-      <c r="H91" t="s">
-        <v>332</v>
-      </c>
       <c r="I91" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J91" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K91" t="s">
         <v>21</v>
@@ -5017,34 +5011,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>331</v>
+      </c>
+      <c r="B92" t="s">
+        <v>332</v>
+      </c>
+      <c r="C92" t="s">
+        <v>36</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" t="s">
         <v>333</v>
       </c>
-      <c r="B92" t="s">
-        <v>334</v>
-      </c>
-      <c r="C92" t="s">
-        <v>49</v>
-      </c>
-      <c r="D92" t="s">
-        <v>14</v>
-      </c>
-      <c r="E92" t="s">
-        <v>50</v>
-      </c>
-      <c r="F92" t="s">
-        <v>32</v>
-      </c>
-      <c r="G92" t="s">
-        <v>33</v>
-      </c>
-      <c r="H92" t="s">
-        <v>335</v>
-      </c>
       <c r="I92" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J92" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K92" t="s">
         <v>21</v>
@@ -5052,34 +5046,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>334</v>
+      </c>
+      <c r="B93" t="s">
+        <v>335</v>
+      </c>
+      <c r="C93" t="s">
         <v>336</v>
       </c>
-      <c r="B93" t="s">
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" t="s">
+        <v>17</v>
+      </c>
+      <c r="H93" t="s">
         <v>337</v>
       </c>
-      <c r="C93" t="s">
-        <v>338</v>
-      </c>
-      <c r="D93" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" t="s">
-        <v>32</v>
-      </c>
-      <c r="G93" t="s">
-        <v>33</v>
-      </c>
-      <c r="H93" t="s">
-        <v>339</v>
-      </c>
       <c r="I93" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J93" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K93" t="s">
         <v>21</v>
@@ -5087,34 +5081,34 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>338</v>
+      </c>
+      <c r="B94" t="s">
+        <v>339</v>
+      </c>
+      <c r="C94" t="s">
+        <v>314</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" t="s">
         <v>340</v>
       </c>
-      <c r="B94" t="s">
-        <v>341</v>
-      </c>
-      <c r="C94" t="s">
-        <v>316</v>
-      </c>
-      <c r="D94" t="s">
-        <v>14</v>
-      </c>
-      <c r="E94" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" t="s">
-        <v>32</v>
-      </c>
-      <c r="G94" t="s">
-        <v>33</v>
-      </c>
-      <c r="H94" t="s">
-        <v>342</v>
-      </c>
       <c r="I94" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J94" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K94" t="s">
         <v>21</v>
@@ -5122,34 +5116,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>341</v>
+      </c>
+      <c r="B95" t="s">
+        <v>342</v>
+      </c>
+      <c r="C95" t="s">
         <v>343</v>
       </c>
-      <c r="B95" t="s">
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" t="s">
         <v>344</v>
       </c>
-      <c r="C95" t="s">
-        <v>345</v>
-      </c>
-      <c r="D95" t="s">
-        <v>14</v>
-      </c>
-      <c r="E95" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" t="s">
-        <v>32</v>
-      </c>
-      <c r="G95" t="s">
-        <v>33</v>
-      </c>
-      <c r="H95" t="s">
-        <v>346</v>
-      </c>
       <c r="I95" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J95" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K95" t="s">
         <v>21</v>
@@ -5157,34 +5151,34 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>345</v>
+      </c>
+      <c r="B96" t="s">
+        <v>346</v>
+      </c>
+      <c r="C96" t="s">
         <v>347</v>
       </c>
-      <c r="B96" t="s">
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" t="s">
         <v>348</v>
       </c>
-      <c r="C96" t="s">
-        <v>349</v>
-      </c>
-      <c r="D96" t="s">
-        <v>14</v>
-      </c>
-      <c r="E96" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" t="s">
-        <v>32</v>
-      </c>
-      <c r="G96" t="s">
-        <v>33</v>
-      </c>
-      <c r="H96" t="s">
-        <v>350</v>
-      </c>
       <c r="I96" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J96" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K96" t="s">
         <v>21</v>
@@ -5192,34 +5186,34 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>349</v>
+      </c>
+      <c r="B97" t="s">
+        <v>350</v>
+      </c>
+      <c r="C97" t="s">
         <v>351</v>
       </c>
-      <c r="B97" t="s">
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" t="s">
+        <v>16</v>
+      </c>
+      <c r="G97" t="s">
+        <v>17</v>
+      </c>
+      <c r="H97" t="s">
         <v>352</v>
       </c>
-      <c r="C97" t="s">
-        <v>353</v>
-      </c>
-      <c r="D97" t="s">
-        <v>14</v>
-      </c>
-      <c r="E97" t="s">
-        <v>15</v>
-      </c>
-      <c r="F97" t="s">
-        <v>32</v>
-      </c>
-      <c r="G97" t="s">
-        <v>33</v>
-      </c>
-      <c r="H97" t="s">
-        <v>354</v>
-      </c>
       <c r="I97" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J97" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K97" t="s">
         <v>21</v>
@@ -5227,34 +5221,34 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>353</v>
+      </c>
+      <c r="B98" t="s">
+        <v>354</v>
+      </c>
+      <c r="C98" t="s">
+        <v>351</v>
+      </c>
+      <c r="D98" t="s">
+        <v>14</v>
+      </c>
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" t="s">
+        <v>17</v>
+      </c>
+      <c r="H98" t="s">
         <v>355</v>
       </c>
-      <c r="B98" t="s">
-        <v>356</v>
-      </c>
-      <c r="C98" t="s">
-        <v>353</v>
-      </c>
-      <c r="D98" t="s">
-        <v>14</v>
-      </c>
-      <c r="E98" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" t="s">
-        <v>32</v>
-      </c>
-      <c r="G98" t="s">
-        <v>33</v>
-      </c>
-      <c r="H98" t="s">
-        <v>357</v>
-      </c>
       <c r="I98" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J98" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K98" t="s">
         <v>21</v>
@@ -5262,34 +5256,34 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>356</v>
+      </c>
+      <c r="B99" t="s">
+        <v>357</v>
+      </c>
+      <c r="C99" t="s">
         <v>358</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D99" t="s">
+        <v>14</v>
+      </c>
+      <c r="E99" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" t="s">
         <v>359</v>
       </c>
-      <c r="C99" t="s">
-        <v>360</v>
-      </c>
-      <c r="D99" t="s">
-        <v>14</v>
-      </c>
-      <c r="E99" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" t="s">
-        <v>32</v>
-      </c>
-      <c r="G99" t="s">
-        <v>33</v>
-      </c>
-      <c r="H99" t="s">
-        <v>361</v>
-      </c>
       <c r="I99" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J99" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K99" t="s">
         <v>21</v>
@@ -5297,34 +5291,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>360</v>
+      </c>
+      <c r="B100" t="s">
+        <v>361</v>
+      </c>
+      <c r="C100" t="s">
         <v>362</v>
       </c>
-      <c r="B100" t="s">
+      <c r="D100" t="s">
+        <v>14</v>
+      </c>
+      <c r="E100" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" t="s">
         <v>363</v>
       </c>
-      <c r="C100" t="s">
-        <v>364</v>
-      </c>
-      <c r="D100" t="s">
-        <v>14</v>
-      </c>
-      <c r="E100" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" t="s">
-        <v>32</v>
-      </c>
-      <c r="G100" t="s">
-        <v>33</v>
-      </c>
-      <c r="H100" t="s">
-        <v>365</v>
-      </c>
       <c r="I100" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J100" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K100" t="s">
         <v>21</v>
@@ -5332,34 +5326,34 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>364</v>
+      </c>
+      <c r="B101" t="s">
+        <v>365</v>
+      </c>
+      <c r="C101" t="s">
         <v>366</v>
       </c>
-      <c r="B101" t="s">
+      <c r="D101" t="s">
+        <v>14</v>
+      </c>
+      <c r="E101" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" t="s">
         <v>367</v>
       </c>
-      <c r="C101" t="s">
-        <v>368</v>
-      </c>
-      <c r="D101" t="s">
-        <v>14</v>
-      </c>
-      <c r="E101" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" t="s">
-        <v>32</v>
-      </c>
-      <c r="G101" t="s">
-        <v>33</v>
-      </c>
-      <c r="H101" t="s">
-        <v>369</v>
-      </c>
       <c r="I101" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J101" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K101" t="s">
         <v>21</v>
@@ -5367,34 +5361,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>368</v>
+      </c>
+      <c r="B102" t="s">
+        <v>369</v>
+      </c>
+      <c r="C102" t="s">
+        <v>366</v>
+      </c>
+      <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" t="s">
         <v>370</v>
       </c>
-      <c r="B102" t="s">
-        <v>371</v>
-      </c>
-      <c r="C102" t="s">
-        <v>368</v>
-      </c>
-      <c r="D102" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" t="s">
-        <v>32</v>
-      </c>
-      <c r="G102" t="s">
-        <v>33</v>
-      </c>
-      <c r="H102" t="s">
-        <v>372</v>
-      </c>
       <c r="I102" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J102" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K102" t="s">
         <v>21</v>
@@ -5402,34 +5396,34 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>371</v>
+      </c>
+      <c r="B103" t="s">
+        <v>372</v>
+      </c>
+      <c r="C103" t="s">
+        <v>366</v>
+      </c>
+      <c r="D103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103" t="s">
         <v>373</v>
       </c>
-      <c r="B103" t="s">
-        <v>374</v>
-      </c>
-      <c r="C103" t="s">
-        <v>368</v>
-      </c>
-      <c r="D103" t="s">
-        <v>14</v>
-      </c>
-      <c r="E103" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" t="s">
-        <v>32</v>
-      </c>
-      <c r="G103" t="s">
-        <v>33</v>
-      </c>
-      <c r="H103" t="s">
-        <v>375</v>
-      </c>
       <c r="I103" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J103" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K103" t="s">
         <v>21</v>
@@ -5437,34 +5431,34 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>374</v>
+      </c>
+      <c r="B104" t="s">
+        <v>375</v>
+      </c>
+      <c r="C104" t="s">
         <v>376</v>
       </c>
-      <c r="B104" t="s">
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" t="s">
+        <v>17</v>
+      </c>
+      <c r="H104" t="s">
         <v>377</v>
       </c>
-      <c r="C104" t="s">
-        <v>378</v>
-      </c>
-      <c r="D104" t="s">
-        <v>14</v>
-      </c>
-      <c r="E104" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" t="s">
-        <v>32</v>
-      </c>
-      <c r="G104" t="s">
-        <v>33</v>
-      </c>
-      <c r="H104" t="s">
-        <v>379</v>
-      </c>
       <c r="I104" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J104" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K104" t="s">
         <v>21</v>
@@ -5472,34 +5466,34 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B105" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" t="s">
         <v>380</v>
       </c>
-      <c r="B105" t="s">
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" t="s">
+        <v>17</v>
+      </c>
+      <c r="H105" t="s">
         <v>381</v>
       </c>
-      <c r="C105" t="s">
-        <v>382</v>
-      </c>
-      <c r="D105" t="s">
-        <v>14</v>
-      </c>
-      <c r="E105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" t="s">
-        <v>32</v>
-      </c>
-      <c r="G105" t="s">
-        <v>33</v>
-      </c>
-      <c r="H105" t="s">
-        <v>383</v>
-      </c>
       <c r="I105" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J105" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K105" t="s">
         <v>21</v>
@@ -5507,34 +5501,34 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>382</v>
+      </c>
+      <c r="B106" t="s">
+        <v>383</v>
+      </c>
+      <c r="C106" t="s">
         <v>384</v>
       </c>
-      <c r="B106" t="s">
+      <c r="D106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" t="s">
+        <v>17</v>
+      </c>
+      <c r="H106" t="s">
         <v>385</v>
       </c>
-      <c r="C106" t="s">
-        <v>386</v>
-      </c>
-      <c r="D106" t="s">
-        <v>14</v>
-      </c>
-      <c r="E106" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" t="s">
-        <v>32</v>
-      </c>
-      <c r="G106" t="s">
-        <v>33</v>
-      </c>
-      <c r="H106" t="s">
-        <v>387</v>
-      </c>
       <c r="I106" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J106" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K106" t="s">
         <v>21</v>
@@ -5542,34 +5536,34 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>386</v>
+      </c>
+      <c r="B107" t="s">
+        <v>387</v>
+      </c>
+      <c r="C107" t="s">
         <v>388</v>
       </c>
-      <c r="B107" t="s">
+      <c r="D107" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" t="s">
+        <v>17</v>
+      </c>
+      <c r="H107" t="s">
         <v>389</v>
       </c>
-      <c r="C107" t="s">
-        <v>390</v>
-      </c>
-      <c r="D107" t="s">
-        <v>14</v>
-      </c>
-      <c r="E107" t="s">
-        <v>15</v>
-      </c>
-      <c r="F107" t="s">
-        <v>32</v>
-      </c>
-      <c r="G107" t="s">
-        <v>33</v>
-      </c>
-      <c r="H107" t="s">
-        <v>391</v>
-      </c>
       <c r="I107" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J107" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K107" t="s">
         <v>21</v>
@@ -5577,34 +5571,34 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>390</v>
+      </c>
+      <c r="B108" t="s">
+        <v>391</v>
+      </c>
+      <c r="C108" t="s">
         <v>392</v>
       </c>
-      <c r="B108" t="s">
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" t="s">
+        <v>17</v>
+      </c>
+      <c r="H108" t="s">
         <v>393</v>
       </c>
-      <c r="C108" t="s">
-        <v>394</v>
-      </c>
-      <c r="D108" t="s">
-        <v>14</v>
-      </c>
-      <c r="E108" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" t="s">
-        <v>32</v>
-      </c>
-      <c r="G108" t="s">
-        <v>33</v>
-      </c>
-      <c r="H108" t="s">
-        <v>395</v>
-      </c>
       <c r="I108" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J108" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K108" t="s">
         <v>21</v>
@@ -5612,34 +5606,34 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>394</v>
+      </c>
+      <c r="B109" t="s">
+        <v>395</v>
+      </c>
+      <c r="C109" t="s">
         <v>396</v>
       </c>
-      <c r="B109" t="s">
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" t="s">
+        <v>17</v>
+      </c>
+      <c r="H109" t="s">
         <v>397</v>
       </c>
-      <c r="C109" t="s">
-        <v>398</v>
-      </c>
-      <c r="D109" t="s">
-        <v>14</v>
-      </c>
-      <c r="E109" t="s">
-        <v>50</v>
-      </c>
-      <c r="F109" t="s">
-        <v>32</v>
-      </c>
-      <c r="G109" t="s">
-        <v>33</v>
-      </c>
-      <c r="H109" t="s">
-        <v>399</v>
-      </c>
       <c r="I109" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J109" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K109" t="s">
         <v>21</v>
@@ -5647,34 +5641,34 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B110" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C110" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D110" t="s">
         <v>14</v>
       </c>
       <c r="E110" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F110" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G110" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H110" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I110" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J110" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K110" t="s">
         <v>21</v>
@@ -5682,34 +5676,34 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>400</v>
+      </c>
+      <c r="B111" t="s">
+        <v>401</v>
+      </c>
+      <c r="C111" t="s">
+        <v>392</v>
+      </c>
+      <c r="D111" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" t="s">
+        <v>17</v>
+      </c>
+      <c r="H111" t="s">
         <v>402</v>
       </c>
-      <c r="B111" t="s">
-        <v>403</v>
-      </c>
-      <c r="C111" t="s">
-        <v>394</v>
-      </c>
-      <c r="D111" t="s">
-        <v>14</v>
-      </c>
-      <c r="E111" t="s">
-        <v>15</v>
-      </c>
-      <c r="F111" t="s">
-        <v>32</v>
-      </c>
-      <c r="G111" t="s">
-        <v>33</v>
-      </c>
-      <c r="H111" t="s">
-        <v>404</v>
-      </c>
       <c r="I111" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J111" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K111" t="s">
         <v>21</v>
@@ -5717,34 +5711,34 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>403</v>
+      </c>
+      <c r="B112" t="s">
+        <v>404</v>
+      </c>
+      <c r="C112" t="s">
         <v>405</v>
       </c>
-      <c r="B112" t="s">
+      <c r="D112" t="s">
+        <v>14</v>
+      </c>
+      <c r="E112" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" t="s">
         <v>406</v>
       </c>
-      <c r="C112" t="s">
+      <c r="G112" t="s">
         <v>407</v>
       </c>
-      <c r="D112" t="s">
-        <v>14</v>
-      </c>
-      <c r="E112" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="H112" t="s">
         <v>408</v>
       </c>
-      <c r="G112" t="s">
-        <v>409</v>
-      </c>
-      <c r="H112" t="s">
-        <v>410</v>
-      </c>
       <c r="I112" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J112" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K112" t="s">
         <v>21</v>
@@ -5752,34 +5746,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>409</v>
+      </c>
+      <c r="B113" t="s">
+        <v>410</v>
+      </c>
+      <c r="C113" t="s">
         <v>411</v>
       </c>
-      <c r="B113" t="s">
+      <c r="D113" t="s">
+        <v>14</v>
+      </c>
+      <c r="E113" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" t="s">
+        <v>17</v>
+      </c>
+      <c r="H113" t="s">
         <v>412</v>
       </c>
-      <c r="C113" t="s">
-        <v>413</v>
-      </c>
-      <c r="D113" t="s">
-        <v>14</v>
-      </c>
-      <c r="E113" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" t="s">
-        <v>32</v>
-      </c>
-      <c r="G113" t="s">
-        <v>33</v>
-      </c>
-      <c r="H113" t="s">
-        <v>414</v>
-      </c>
       <c r="I113" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J113" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K113" t="s">
         <v>21</v>
@@ -5787,34 +5781,34 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>413</v>
+      </c>
+      <c r="B114" t="s">
+        <v>414</v>
+      </c>
+      <c r="C114" t="s">
+        <v>392</v>
+      </c>
+      <c r="D114" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" t="s">
+        <v>17</v>
+      </c>
+      <c r="H114" t="s">
         <v>415</v>
       </c>
-      <c r="B114" t="s">
-        <v>416</v>
-      </c>
-      <c r="C114" t="s">
-        <v>394</v>
-      </c>
-      <c r="D114" t="s">
-        <v>14</v>
-      </c>
-      <c r="E114" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" t="s">
-        <v>32</v>
-      </c>
-      <c r="G114" t="s">
-        <v>33</v>
-      </c>
-      <c r="H114" t="s">
-        <v>417</v>
-      </c>
       <c r="I114" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J114" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K114" t="s">
         <v>21</v>
@@ -5822,34 +5816,34 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>416</v>
+      </c>
+      <c r="B115" t="s">
+        <v>417</v>
+      </c>
+      <c r="C115" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s">
+        <v>14</v>
+      </c>
+      <c r="E115" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" t="s">
+        <v>17</v>
+      </c>
+      <c r="H115" t="s">
         <v>418</v>
       </c>
-      <c r="B115" t="s">
-        <v>419</v>
-      </c>
-      <c r="C115" t="s">
-        <v>49</v>
-      </c>
-      <c r="D115" t="s">
-        <v>14</v>
-      </c>
-      <c r="E115" t="s">
-        <v>50</v>
-      </c>
-      <c r="F115" t="s">
-        <v>32</v>
-      </c>
-      <c r="G115" t="s">
-        <v>33</v>
-      </c>
-      <c r="H115" t="s">
-        <v>420</v>
-      </c>
       <c r="I115" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J115" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K115" t="s">
         <v>21</v>
@@ -5857,10 +5851,10 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B116" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C116" t="s">
         <v>67</v>
@@ -5872,19 +5866,19 @@
         <v>15</v>
       </c>
       <c r="F116" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G116" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H116" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="I116" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J116" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K116" t="s">
         <v>21</v>
@@ -5892,10 +5886,10 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B117" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C117" t="s">
         <v>67</v>
@@ -5907,19 +5901,19 @@
         <v>15</v>
       </c>
       <c r="F117" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G117" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H117" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="I117" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J117" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K117" t="s">
         <v>21</v>
@@ -5927,10 +5921,10 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B118" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C118" t="s">
         <v>67</v>
@@ -5942,19 +5936,19 @@
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G118" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H118" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="I118" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K118" t="s">
         <v>21</v>
@@ -5962,34 +5956,34 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>428</v>
+      </c>
+      <c r="B119" t="s">
+        <v>429</v>
+      </c>
+      <c r="C119" t="s">
         <v>430</v>
       </c>
-      <c r="B119" t="s">
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" t="s">
+        <v>17</v>
+      </c>
+      <c r="H119" t="s">
         <v>431</v>
       </c>
-      <c r="C119" t="s">
-        <v>432</v>
-      </c>
-      <c r="D119" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" t="s">
-        <v>32</v>
-      </c>
-      <c r="G119" t="s">
-        <v>33</v>
-      </c>
-      <c r="H119" t="s">
-        <v>433</v>
-      </c>
       <c r="I119" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J119" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K119" t="s">
         <v>21</v>
@@ -5997,34 +5991,34 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>432</v>
+      </c>
+      <c r="B120" t="s">
+        <v>433</v>
+      </c>
+      <c r="C120" t="s">
+        <v>430</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" t="s">
+        <v>17</v>
+      </c>
+      <c r="H120" t="s">
         <v>434</v>
       </c>
-      <c r="B120" t="s">
-        <v>435</v>
-      </c>
-      <c r="C120" t="s">
-        <v>432</v>
-      </c>
-      <c r="D120" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" t="s">
-        <v>32</v>
-      </c>
-      <c r="G120" t="s">
-        <v>33</v>
-      </c>
-      <c r="H120" t="s">
-        <v>436</v>
-      </c>
       <c r="I120" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J120" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K120" t="s">
         <v>21</v>
@@ -6032,34 +6026,34 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>435</v>
+      </c>
+      <c r="B121" t="s">
+        <v>436</v>
+      </c>
+      <c r="C121" t="s">
+        <v>430</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" t="s">
+        <v>17</v>
+      </c>
+      <c r="H121" t="s">
         <v>437</v>
       </c>
-      <c r="B121" t="s">
-        <v>438</v>
-      </c>
-      <c r="C121" t="s">
-        <v>432</v>
-      </c>
-      <c r="D121" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>32</v>
-      </c>
-      <c r="G121" t="s">
-        <v>33</v>
-      </c>
-      <c r="H121" t="s">
-        <v>439</v>
-      </c>
       <c r="I121" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J121" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K121" t="s">
         <v>21</v>
@@ -6067,34 +6061,34 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>438</v>
+      </c>
+      <c r="B122" t="s">
+        <v>439</v>
+      </c>
+      <c r="C122" t="s">
         <v>440</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" t="s">
+        <v>17</v>
+      </c>
+      <c r="H122" t="s">
         <v>441</v>
       </c>
-      <c r="C122" t="s">
-        <v>442</v>
-      </c>
-      <c r="D122" t="s">
-        <v>14</v>
-      </c>
-      <c r="E122" t="s">
-        <v>15</v>
-      </c>
-      <c r="F122" t="s">
-        <v>32</v>
-      </c>
-      <c r="G122" t="s">
-        <v>33</v>
-      </c>
-      <c r="H122" t="s">
-        <v>443</v>
-      </c>
       <c r="I122" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J122" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K122" t="s">
         <v>21</v>
@@ -6102,10 +6096,10 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B123" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C123" t="s">
         <v>67</v>
@@ -6117,19 +6111,19 @@
         <v>15</v>
       </c>
       <c r="F123" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G123" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H123" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I123" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J123" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K123" t="s">
         <v>21</v>
@@ -6137,10 +6131,10 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B124" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C124" t="s">
         <v>67</v>
@@ -6152,19 +6146,19 @@
         <v>15</v>
       </c>
       <c r="F124" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G124" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H124" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="I124" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J124" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K124" t="s">
         <v>21</v>
@@ -6172,34 +6166,34 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>448</v>
+      </c>
+      <c r="B125" t="s">
+        <v>449</v>
+      </c>
+      <c r="C125" t="s">
         <v>450</v>
       </c>
-      <c r="B125" t="s">
+      <c r="D125" t="s">
+        <v>14</v>
+      </c>
+      <c r="E125" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" t="s">
+        <v>17</v>
+      </c>
+      <c r="H125" t="s">
         <v>451</v>
       </c>
-      <c r="C125" t="s">
-        <v>452</v>
-      </c>
-      <c r="D125" t="s">
-        <v>14</v>
-      </c>
-      <c r="E125" t="s">
-        <v>15</v>
-      </c>
-      <c r="F125" t="s">
-        <v>32</v>
-      </c>
-      <c r="G125" t="s">
-        <v>33</v>
-      </c>
-      <c r="H125" t="s">
-        <v>453</v>
-      </c>
       <c r="I125" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J125" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K125" t="s">
         <v>21</v>
@@ -6207,10 +6201,10 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B126" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C126" t="s">
         <v>67</v>
@@ -6222,19 +6216,19 @@
         <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G126" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H126" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I126" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J126" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K126" t="s">
         <v>21</v>
@@ -6242,34 +6236,34 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>455</v>
+      </c>
+      <c r="B127" t="s">
+        <v>456</v>
+      </c>
+      <c r="C127" t="s">
         <v>457</v>
       </c>
-      <c r="B127" t="s">
+      <c r="D127" t="s">
+        <v>14</v>
+      </c>
+      <c r="E127" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" t="s">
         <v>458</v>
       </c>
-      <c r="C127" t="s">
-        <v>459</v>
-      </c>
-      <c r="D127" t="s">
-        <v>14</v>
-      </c>
-      <c r="E127" t="s">
-        <v>15</v>
-      </c>
-      <c r="F127" t="s">
-        <v>32</v>
-      </c>
-      <c r="G127" t="s">
-        <v>33</v>
-      </c>
-      <c r="H127" t="s">
-        <v>460</v>
-      </c>
       <c r="I127" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J127" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K127" t="s">
         <v>21</v>
@@ -6277,34 +6271,34 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>459</v>
+      </c>
+      <c r="B128" t="s">
+        <v>460</v>
+      </c>
+      <c r="C128" t="s">
+        <v>440</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" t="s">
+        <v>17</v>
+      </c>
+      <c r="H128" t="s">
         <v>461</v>
       </c>
-      <c r="B128" t="s">
-        <v>462</v>
-      </c>
-      <c r="C128" t="s">
-        <v>442</v>
-      </c>
-      <c r="D128" t="s">
-        <v>14</v>
-      </c>
-      <c r="E128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>32</v>
-      </c>
-      <c r="G128" t="s">
-        <v>33</v>
-      </c>
-      <c r="H128" t="s">
-        <v>463</v>
-      </c>
       <c r="I128" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J128" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K128" t="s">
         <v>21</v>
@@ -6312,34 +6306,34 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>462</v>
+      </c>
+      <c r="B129" t="s">
+        <v>463</v>
+      </c>
+      <c r="C129" t="s">
+        <v>36</v>
+      </c>
+      <c r="D129" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" t="s">
+        <v>37</v>
+      </c>
+      <c r="F129" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" t="s">
+        <v>17</v>
+      </c>
+      <c r="H129" t="s">
         <v>464</v>
       </c>
-      <c r="B129" t="s">
-        <v>465</v>
-      </c>
-      <c r="C129" t="s">
-        <v>49</v>
-      </c>
-      <c r="D129" t="s">
-        <v>14</v>
-      </c>
-      <c r="E129" t="s">
-        <v>50</v>
-      </c>
-      <c r="F129" t="s">
-        <v>32</v>
-      </c>
-      <c r="G129" t="s">
-        <v>33</v>
-      </c>
-      <c r="H129" t="s">
-        <v>466</v>
-      </c>
       <c r="I129" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J129" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K129" t="s">
         <v>21</v>
@@ -6347,34 +6341,34 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>465</v>
+      </c>
+      <c r="B130" t="s">
+        <v>466</v>
+      </c>
+      <c r="C130" t="s">
+        <v>440</v>
+      </c>
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" t="s">
+        <v>17</v>
+      </c>
+      <c r="H130" t="s">
         <v>467</v>
       </c>
-      <c r="B130" t="s">
-        <v>468</v>
-      </c>
-      <c r="C130" t="s">
-        <v>442</v>
-      </c>
-      <c r="D130" t="s">
-        <v>14</v>
-      </c>
-      <c r="E130" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" t="s">
-        <v>32</v>
-      </c>
-      <c r="G130" t="s">
-        <v>33</v>
-      </c>
-      <c r="H130" t="s">
-        <v>469</v>
-      </c>
       <c r="I130" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J130" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K130" t="s">
         <v>21</v>
@@ -6382,10 +6376,10 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B131" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C131" t="s">
         <v>67</v>
@@ -6397,19 +6391,19 @@
         <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G131" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H131" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="I131" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J131" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K131" t="s">
         <v>21</v>
@@ -6417,34 +6411,34 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>471</v>
+      </c>
+      <c r="B132" t="s">
+        <v>472</v>
+      </c>
+      <c r="C132" t="s">
+        <v>440</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" t="s">
+        <v>16</v>
+      </c>
+      <c r="G132" t="s">
+        <v>17</v>
+      </c>
+      <c r="H132" t="s">
         <v>473</v>
       </c>
-      <c r="B132" t="s">
-        <v>474</v>
-      </c>
-      <c r="C132" t="s">
-        <v>442</v>
-      </c>
-      <c r="D132" t="s">
-        <v>14</v>
-      </c>
-      <c r="E132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" t="s">
-        <v>32</v>
-      </c>
-      <c r="G132" t="s">
-        <v>33</v>
-      </c>
-      <c r="H132" t="s">
-        <v>475</v>
-      </c>
       <c r="I132" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J132" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K132" t="s">
         <v>21</v>
@@ -6452,34 +6446,34 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>474</v>
+      </c>
+      <c r="B133" t="s">
+        <v>475</v>
+      </c>
+      <c r="C133" t="s">
+        <v>440</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133" t="s">
         <v>476</v>
       </c>
-      <c r="B133" t="s">
-        <v>477</v>
-      </c>
-      <c r="C133" t="s">
-        <v>442</v>
-      </c>
-      <c r="D133" t="s">
-        <v>14</v>
-      </c>
-      <c r="E133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>32</v>
-      </c>
-      <c r="G133" t="s">
-        <v>33</v>
-      </c>
-      <c r="H133" t="s">
-        <v>478</v>
-      </c>
       <c r="I133" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="J133" t="s">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="K133" t="s">
         <v>21</v>
